--- a/Journal-de-Travail_MatiasDenis.xlsx
+++ b/Journal-de-Travail_MatiasDenis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05-repertoires-ict-ssd (2022)\Deuxième année\P_AppMobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_README\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20068F-0D8A-4074-81DA-D972774F8FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DA9768-39E5-4E43-AB51-71216A74308F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="33705" yWindow="1620" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Création de la maquette high-fidelity sur Figma, regroupant les fonctionnalités demandées dans le cahier des charges.</t>
+  </si>
+  <si>
+    <t>Absence - Maladie.</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1051,7 @@
                   <c:v>1.0416666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.7361111111111112E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2008,7 +2011,7 @@
       </c>
       <c r="C3" s="25" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 3 heurs 15 minutes</v>
+        <v>0 jours 6 heurs 40 minutes</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="3"/>
@@ -2023,15 +2026,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="25">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="D4" s="25">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E4" s="52">
         <f>SUM(C4:D4)</f>
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2116,11 +2119,21 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="18"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="48"/>
+      <c r="B9" s="40">
+        <v>46055</v>
+      </c>
+      <c r="C9" s="36">
+        <v>3</v>
+      </c>
+      <c r="D9" s="44">
+        <v>25</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="20"/>
       <c r="M9" t="s">
         <v>4</v>
@@ -8253,7 +8266,7 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C11,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C11" s="51" t="str">
         <f>'Journal de travail'!M15</f>
@@ -8261,7 +8274,7 @@
       </c>
       <c r="D11" s="45">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7361111111111112E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -8270,7 +8283,7 @@
       </c>
       <c r="D12" s="46">
         <f>SUM(D4:D11)</f>
-        <v>5.2083333333333329E-2</v>
+        <v>6.9444444444444448E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -8283,14 +8296,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8501,23 +8512,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
-    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8542,9 +8550,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
+    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Journal-de-Travail_MatiasDenis.xlsx
+++ b/Journal-de-Travail_MatiasDenis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_README\P_AppMobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_README\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DA9768-39E5-4E43-AB51-71216A74308F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32DFDC-36AC-49CA-9C46-E8AB8E886B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33705" yWindow="1620" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="32040" yWindow="1020" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -140,6 +140,53 @@
   <si>
     <t>Absence - Maladie.</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Initialisation de la base de données : modification de la migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>books</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et du modèle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Book</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pour supporter le stockage binaire (MEDIUMBLOB) des fichiers ePub et des couvertures.</t>
+    </r>
+  </si>
+  <si>
+    <t>Il a été nécessaire de reprendre ce qui avait été déjà fait afin de faire une mise à jour sur l'avancée jusqu'à maintenant car j'étais un peu perdu après mon absence du lundi 2 février. En utilisant l'IA j'ai pu mieux comprendre ce qui était demandé dans le cahier des charges par rapport à ce projet. J'ai dû créé un nouveau clone du repo en local et étudier le code afin de me réperer sur ce qui était nécessaire de faire. J'ai également retouché la maquette pour être en accord avec ce qui est demandé dans le cahier des charges</t>
+  </si>
+  <si>
+    <t>Correction de l'arborescence des fichiers et importation réussie de la bibliothèque complète (6 livres) en format binaire (MEDIUMBLOB) dans MySQL via le BookSeeder.</t>
+  </si>
 </sst>
 </file>
 
@@ -153,7 +200,7 @@
     <numFmt numFmtId="168" formatCode="00\ &quot;min&quot;"/>
     <numFmt numFmtId="169" formatCode="hh\ &quot;h&quot;\ mm\ &quot;min&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -231,6 +278,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1030,10 +1082,10 @@
                 <c:formatCode>hh\ "h"\ mm\ "min"</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>4.1666666666666664E-2</c:v>
+                  <c:v>0.10416666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4.1666666666666664E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1961,7 +2013,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF2E8F1-C793-7E43-B3DE-C075053A97DA}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O532"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.75" style="8" customWidth="1"/>
     <col min="2" max="2" width="9.75" style="1" customWidth="1"/>
@@ -1978,7 +2030,7 @@
     <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="23.25">
       <c r="A1" s="9"/>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
@@ -1989,7 +2041,7 @@
       </c>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="23.25">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2005,13 +2057,13 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="23.25">
       <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="25" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 6 heurs 40 minutes</v>
+        <v>0 jours 9 heurs 9 minutes</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="3"/>
@@ -2022,30 +2074,30 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="23.25" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="23.25" hidden="1">
       <c r="B4" s="5"/>
       <c r="C4" s="25">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="D4" s="25">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="E4" s="52">
         <f>SUM(C4:D4)</f>
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="C5" s="55" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="55"/>
     </row>
-    <row r="6" spans="1:15" s="23" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="23" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A6" s="21" t="s">
         <v>11</v>
       </c>
@@ -2068,7 +2120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="31.5">
       <c r="A7" s="14">
         <f>IF(ISBLANK(B7),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B7))</f>
         <v>5</v>
@@ -2088,7 +2140,7 @@
       </c>
       <c r="G7" s="16"/>
     </row>
-    <row r="8" spans="1:15" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="31.5">
       <c r="B8" s="39">
         <v>46048</v>
       </c>
@@ -2117,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" s="18"/>
       <c r="B9" s="40">
         <v>46055</v>
@@ -2145,11 +2197,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="39"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="43"/>
-      <c r="F10" s="48"/>
+    <row r="10" spans="1:15" ht="94.5">
+      <c r="B10" s="39">
+        <v>46062</v>
+      </c>
+      <c r="C10" s="35">
+        <v>1</v>
+      </c>
+      <c r="D10" s="43">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="G10" s="17"/>
       <c r="M10" t="s">
         <v>5</v>
@@ -2161,13 +2224,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="31.5">
       <c r="A11" s="18"/>
-      <c r="B11" s="40"/>
+      <c r="B11" s="40">
+        <v>46062</v>
+      </c>
       <c r="C11" s="36"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="48"/>
+      <c r="D11" s="44">
+        <v>45</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>33</v>
+      </c>
       <c r="G11" s="20"/>
       <c r="M11" t="s">
         <v>6</v>
@@ -2179,11 +2250,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="39"/>
+    <row r="12" spans="1:15">
+      <c r="B12" s="39">
+        <v>46062</v>
+      </c>
       <c r="C12" s="35"/>
-      <c r="D12" s="43"/>
-      <c r="F12" s="48"/>
+      <c r="D12" s="43">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
       <c r="G12" s="17"/>
       <c r="M12" t="s">
         <v>7</v>
@@ -2195,7 +2275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13" s="18"/>
       <c r="B13" s="40"/>
       <c r="C13" s="36"/>
@@ -2213,7 +2293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="B14" s="39"/>
       <c r="C14" s="35"/>
       <c r="D14" s="43"/>
@@ -2229,7 +2309,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15" s="18"/>
       <c r="B15" s="40"/>
       <c r="C15" s="36"/>
@@ -2247,7 +2327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="B16" s="39"/>
       <c r="C16" s="35"/>
       <c r="D16" s="43"/>
@@ -2257,7 +2337,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17" s="18"/>
       <c r="B17" s="40"/>
       <c r="C17" s="36"/>
@@ -2269,7 +2349,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="B18" s="39"/>
       <c r="C18" s="35"/>
       <c r="D18" s="43"/>
@@ -2279,7 +2359,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19" s="18"/>
       <c r="B19" s="40"/>
       <c r="C19" s="36"/>
@@ -2291,14 +2371,14 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15">
       <c r="B20" s="39"/>
       <c r="C20" s="35"/>
       <c r="D20" s="43"/>
       <c r="F20" s="48"/>
       <c r="G20" s="17"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21" s="18"/>
       <c r="B21" s="40"/>
       <c r="C21" s="36"/>
@@ -2307,14 +2387,14 @@
       <c r="F21" s="48"/>
       <c r="G21" s="20"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="B22" s="39"/>
       <c r="C22" s="35"/>
       <c r="D22" s="43"/>
       <c r="F22" s="48"/>
       <c r="G22" s="17"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" s="18"/>
       <c r="B23" s="40"/>
       <c r="C23" s="36"/>
@@ -2323,14 +2403,14 @@
       <c r="F23" s="48"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="B24" s="39"/>
       <c r="C24" s="35"/>
       <c r="D24" s="43"/>
       <c r="F24" s="48"/>
       <c r="G24" s="17"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25" s="18"/>
       <c r="B25" s="40"/>
       <c r="C25" s="36"/>
@@ -2339,14 +2419,14 @@
       <c r="F25" s="48"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="B26" s="39"/>
       <c r="C26" s="35"/>
       <c r="D26" s="43"/>
       <c r="F26" s="48"/>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27" s="18"/>
       <c r="B27" s="40"/>
       <c r="C27" s="36"/>
@@ -2355,14 +2435,14 @@
       <c r="F27" s="48"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="B28" s="39"/>
       <c r="C28" s="35"/>
       <c r="D28" s="43"/>
       <c r="F28" s="47"/>
       <c r="G28" s="17"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29" s="18"/>
       <c r="B29" s="40"/>
       <c r="C29" s="36"/>
@@ -2371,14 +2451,14 @@
       <c r="F29" s="47"/>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="B30" s="39"/>
       <c r="C30" s="35"/>
       <c r="D30" s="43"/>
       <c r="F30" s="48"/>
       <c r="G30" s="17"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31" s="18"/>
       <c r="B31" s="40"/>
       <c r="C31" s="36"/>
@@ -2387,14 +2467,14 @@
       <c r="F31" s="47"/>
       <c r="G31" s="20"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="B32" s="39"/>
       <c r="C32" s="35"/>
       <c r="D32" s="43"/>
       <c r="F32" s="48"/>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" s="18"/>
       <c r="B33" s="40"/>
       <c r="C33" s="36"/>
@@ -2403,14 +2483,14 @@
       <c r="F33" s="47"/>
       <c r="G33" s="20"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="B34" s="39"/>
       <c r="C34" s="35"/>
       <c r="D34" s="43"/>
       <c r="F34" s="47"/>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" s="18"/>
       <c r="B35" s="40"/>
       <c r="C35" s="36"/>
@@ -2419,14 +2499,14 @@
       <c r="F35" s="48"/>
       <c r="G35" s="20"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="B36" s="39"/>
       <c r="C36" s="35"/>
       <c r="D36" s="43"/>
       <c r="F36" s="47"/>
       <c r="G36" s="17"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="18"/>
       <c r="B37" s="40"/>
       <c r="C37" s="36"/>
@@ -2435,14 +2515,14 @@
       <c r="F37" s="47"/>
       <c r="G37" s="20"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="B38" s="39"/>
       <c r="C38" s="35"/>
       <c r="D38" s="43"/>
       <c r="F38" s="47"/>
       <c r="G38" s="17"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="18"/>
       <c r="B39" s="40"/>
       <c r="C39" s="36"/>
@@ -2451,14 +2531,14 @@
       <c r="F39" s="47"/>
       <c r="G39" s="20"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="B40" s="39"/>
       <c r="C40" s="35"/>
       <c r="D40" s="43"/>
       <c r="F40" s="47"/>
       <c r="G40" s="17"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="18"/>
       <c r="B41" s="40"/>
       <c r="C41" s="36"/>
@@ -2467,14 +2547,14 @@
       <c r="F41" s="47"/>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="B42" s="39"/>
       <c r="C42" s="35"/>
       <c r="D42" s="43"/>
       <c r="F42" s="47"/>
       <c r="G42" s="17"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="18"/>
       <c r="B43" s="40"/>
       <c r="C43" s="36"/>
@@ -2483,14 +2563,14 @@
       <c r="F43" s="47"/>
       <c r="G43" s="20"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="B44" s="39"/>
       <c r="C44" s="35"/>
       <c r="D44" s="43"/>
       <c r="F44" s="47"/>
       <c r="G44" s="17"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" s="18"/>
       <c r="B45" s="40"/>
       <c r="C45" s="36"/>
@@ -2499,14 +2579,14 @@
       <c r="F45" s="47"/>
       <c r="G45" s="20"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="B46" s="39"/>
       <c r="C46" s="35"/>
       <c r="D46" s="43"/>
       <c r="F46" s="47"/>
       <c r="G46" s="17"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="18"/>
       <c r="B47" s="40"/>
       <c r="C47" s="36"/>
@@ -2515,14 +2595,14 @@
       <c r="F47" s="47"/>
       <c r="G47" s="20"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="B48" s="39"/>
       <c r="C48" s="35"/>
       <c r="D48" s="43"/>
       <c r="F48" s="47"/>
       <c r="G48" s="17"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="18"/>
       <c r="B49" s="40"/>
       <c r="C49" s="36"/>
@@ -2531,14 +2611,14 @@
       <c r="F49" s="47"/>
       <c r="G49" s="20"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="B50" s="39"/>
       <c r="C50" s="35"/>
       <c r="D50" s="43"/>
       <c r="F50" s="47"/>
       <c r="G50" s="17"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" s="18"/>
       <c r="B51" s="40"/>
       <c r="C51" s="36"/>
@@ -2547,14 +2627,14 @@
       <c r="F51" s="47"/>
       <c r="G51" s="20"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="B52" s="39"/>
       <c r="C52" s="35"/>
       <c r="D52" s="43"/>
       <c r="F52" s="47"/>
       <c r="G52" s="17"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" s="18"/>
       <c r="B53" s="40"/>
       <c r="C53" s="36"/>
@@ -2563,14 +2643,14 @@
       <c r="F53" s="47"/>
       <c r="G53" s="20"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="B54" s="39"/>
       <c r="C54" s="35"/>
       <c r="D54" s="43"/>
       <c r="F54" s="47"/>
       <c r="G54" s="17"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" s="18"/>
       <c r="B55" s="40"/>
       <c r="C55" s="36"/>
@@ -2579,7 +2659,7 @@
       <c r="F55" s="47"/>
       <c r="G55" s="20"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="8" t="str">
         <f>IF(ISBLANK(B56),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B56))</f>
         <v/>
@@ -2590,7 +2670,7 @@
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" s="18" t="str">
         <f>IF(ISBLANK(B57),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B57))</f>
         <v/>
@@ -2602,7 +2682,7 @@
       <c r="F57" s="20"/>
       <c r="G57" s="20"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" s="8" t="str">
         <f>IF(ISBLANK(B58),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B58))</f>
         <v/>
@@ -2613,7 +2693,7 @@
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" s="18" t="str">
         <f>IF(ISBLANK(B59),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B59))</f>
         <v/>
@@ -2625,7 +2705,7 @@
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" s="8" t="str">
         <f>IF(ISBLANK(B60),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B60))</f>
         <v/>
@@ -2636,7 +2716,7 @@
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" s="18" t="str">
         <f>IF(ISBLANK(B61),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B61))</f>
         <v/>
@@ -2648,7 +2728,7 @@
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" s="8" t="str">
         <f>IF(ISBLANK(B62),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B62))</f>
         <v/>
@@ -2659,7 +2739,7 @@
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" s="18" t="str">
         <f>IF(ISBLANK(B63),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B63))</f>
         <v/>
@@ -2671,7 +2751,7 @@
       <c r="F63" s="20"/>
       <c r="G63" s="20"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" s="8" t="str">
         <f>IF(ISBLANK(B64),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B64))</f>
         <v/>
@@ -2682,7 +2762,7 @@
       <c r="F64" s="17"/>
       <c r="G64" s="17"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" s="18" t="str">
         <f>IF(ISBLANK(B65),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B65))</f>
         <v/>
@@ -2694,7 +2774,7 @@
       <c r="F65" s="20"/>
       <c r="G65" s="20"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" s="8" t="str">
         <f>IF(ISBLANK(B66),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B66))</f>
         <v/>
@@ -2705,7 +2785,7 @@
       <c r="F66" s="17"/>
       <c r="G66" s="17"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" s="18" t="str">
         <f>IF(ISBLANK(B67),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B67))</f>
         <v/>
@@ -2717,7 +2797,7 @@
       <c r="F67" s="20"/>
       <c r="G67" s="20"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" s="8" t="str">
         <f>IF(ISBLANK(B68),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B68))</f>
         <v/>
@@ -2728,7 +2808,7 @@
       <c r="F68" s="17"/>
       <c r="G68" s="17"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" s="18" t="str">
         <f>IF(ISBLANK(B69),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B69))</f>
         <v/>
@@ -2740,7 +2820,7 @@
       <c r="F69" s="20"/>
       <c r="G69" s="20"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" s="8" t="str">
         <f>IF(ISBLANK(B70),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B70))</f>
         <v/>
@@ -2751,7 +2831,7 @@
       <c r="F70" s="17"/>
       <c r="G70" s="17"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="18" t="str">
         <f>IF(ISBLANK(B71),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B71))</f>
         <v/>
@@ -2763,7 +2843,7 @@
       <c r="F71" s="20"/>
       <c r="G71" s="20"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" s="8" t="str">
         <f>IF(ISBLANK(B72),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B72))</f>
         <v/>
@@ -2774,7 +2854,7 @@
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="18" t="str">
         <f>IF(ISBLANK(B73),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B73))</f>
         <v/>
@@ -2786,7 +2866,7 @@
       <c r="F73" s="20"/>
       <c r="G73" s="20"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="8" t="str">
         <f>IF(ISBLANK(B74),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B74))</f>
         <v/>
@@ -2797,7 +2877,7 @@
       <c r="F74" s="17"/>
       <c r="G74" s="17"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="18" t="str">
         <f>IF(ISBLANK(B75),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B75))</f>
         <v/>
@@ -2809,7 +2889,7 @@
       <c r="F75" s="20"/>
       <c r="G75" s="20"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="8" t="str">
         <f>IF(ISBLANK(B76),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B76))</f>
         <v/>
@@ -2820,7 +2900,7 @@
       <c r="F76" s="17"/>
       <c r="G76" s="17"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="18" t="str">
         <f>IF(ISBLANK(B77),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B77))</f>
         <v/>
@@ -2832,7 +2912,7 @@
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" s="8" t="str">
         <f>IF(ISBLANK(B78),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B78))</f>
         <v/>
@@ -2843,7 +2923,7 @@
       <c r="F78" s="17"/>
       <c r="G78" s="17"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="18" t="str">
         <f>IF(ISBLANK(B79),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B79))</f>
         <v/>
@@ -2855,7 +2935,7 @@
       <c r="F79" s="20"/>
       <c r="G79" s="20"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="8" t="str">
         <f>IF(ISBLANK(B80),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B80))</f>
         <v/>
@@ -2866,7 +2946,7 @@
       <c r="F80" s="17"/>
       <c r="G80" s="17"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7">
       <c r="A81" s="18" t="str">
         <f>IF(ISBLANK(B81),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B81))</f>
         <v/>
@@ -2878,7 +2958,7 @@
       <c r="F81" s="20"/>
       <c r="G81" s="20"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7">
       <c r="A82" s="8" t="str">
         <f>IF(ISBLANK(B82),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B82))</f>
         <v/>
@@ -2889,7 +2969,7 @@
       <c r="F82" s="17"/>
       <c r="G82" s="17"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="18" t="str">
         <f>IF(ISBLANK(B83),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B83))</f>
         <v/>
@@ -2901,7 +2981,7 @@
       <c r="F83" s="20"/>
       <c r="G83" s="20"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7">
       <c r="A84" s="8" t="str">
         <f>IF(ISBLANK(B84),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B84))</f>
         <v/>
@@ -2912,7 +2992,7 @@
       <c r="F84" s="17"/>
       <c r="G84" s="17"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7">
       <c r="A85" s="18" t="str">
         <f>IF(ISBLANK(B85),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B85))</f>
         <v/>
@@ -2924,7 +3004,7 @@
       <c r="F85" s="20"/>
       <c r="G85" s="20"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7">
       <c r="A86" s="8" t="str">
         <f>IF(ISBLANK(B86),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B86))</f>
         <v/>
@@ -2935,7 +3015,7 @@
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="18" t="str">
         <f>IF(ISBLANK(B87),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B87))</f>
         <v/>
@@ -2947,7 +3027,7 @@
       <c r="F87" s="20"/>
       <c r="G87" s="20"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="8" t="str">
         <f>IF(ISBLANK(B88),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B88))</f>
         <v/>
@@ -2958,7 +3038,7 @@
       <c r="F88" s="17"/>
       <c r="G88" s="17"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7">
       <c r="A89" s="18" t="str">
         <f>IF(ISBLANK(B89),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B89))</f>
         <v/>
@@ -2970,7 +3050,7 @@
       <c r="F89" s="20"/>
       <c r="G89" s="20"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7">
       <c r="A90" s="8" t="str">
         <f>IF(ISBLANK(B90),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B90))</f>
         <v/>
@@ -2981,7 +3061,7 @@
       <c r="F90" s="17"/>
       <c r="G90" s="17"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="18" t="str">
         <f>IF(ISBLANK(B91),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B91))</f>
         <v/>
@@ -2993,7 +3073,7 @@
       <c r="F91" s="20"/>
       <c r="G91" s="20"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="8" t="str">
         <f>IF(ISBLANK(B92),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B92))</f>
         <v/>
@@ -3004,7 +3084,7 @@
       <c r="F92" s="17"/>
       <c r="G92" s="17"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7">
       <c r="A93" s="18" t="str">
         <f>IF(ISBLANK(B93),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B93))</f>
         <v/>
@@ -3016,7 +3096,7 @@
       <c r="F93" s="20"/>
       <c r="G93" s="20"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="8" t="str">
         <f>IF(ISBLANK(B94),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B94))</f>
         <v/>
@@ -3027,7 +3107,7 @@
       <c r="F94" s="17"/>
       <c r="G94" s="17"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="18" t="str">
         <f>IF(ISBLANK(B95),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B95))</f>
         <v/>
@@ -3039,7 +3119,7 @@
       <c r="F95" s="20"/>
       <c r="G95" s="20"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7">
       <c r="A96" s="8" t="str">
         <f>IF(ISBLANK(B96),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B96))</f>
         <v/>
@@ -3050,7 +3130,7 @@
       <c r="F96" s="17"/>
       <c r="G96" s="17"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97" s="18" t="str">
         <f>IF(ISBLANK(B97),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B97))</f>
         <v/>
@@ -3062,7 +3142,7 @@
       <c r="F97" s="20"/>
       <c r="G97" s="20"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="8" t="str">
         <f>IF(ISBLANK(B98),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B98))</f>
         <v/>
@@ -3073,7 +3153,7 @@
       <c r="F98" s="17"/>
       <c r="G98" s="17"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7">
       <c r="A99" s="18" t="str">
         <f>IF(ISBLANK(B99),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B99))</f>
         <v/>
@@ -3085,7 +3165,7 @@
       <c r="F99" s="20"/>
       <c r="G99" s="20"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7">
       <c r="A100" s="8" t="str">
         <f>IF(ISBLANK(B100),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B100))</f>
         <v/>
@@ -3096,7 +3176,7 @@
       <c r="F100" s="17"/>
       <c r="G100" s="17"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7">
       <c r="A101" s="18" t="str">
         <f>IF(ISBLANK(B101),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B101))</f>
         <v/>
@@ -3108,7 +3188,7 @@
       <c r="F101" s="20"/>
       <c r="G101" s="20"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="8" t="str">
         <f>IF(ISBLANK(B102),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B102))</f>
         <v/>
@@ -3119,7 +3199,7 @@
       <c r="F102" s="17"/>
       <c r="G102" s="17"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7">
       <c r="A103" s="18" t="str">
         <f>IF(ISBLANK(B103),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B103))</f>
         <v/>
@@ -3131,7 +3211,7 @@
       <c r="F103" s="20"/>
       <c r="G103" s="20"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7">
       <c r="A104" s="8" t="str">
         <f>IF(ISBLANK(B104),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B104))</f>
         <v/>
@@ -3142,7 +3222,7 @@
       <c r="F104" s="17"/>
       <c r="G104" s="17"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="18" t="str">
         <f>IF(ISBLANK(B105),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B105))</f>
         <v/>
@@ -3154,7 +3234,7 @@
       <c r="F105" s="20"/>
       <c r="G105" s="20"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106" s="8" t="str">
         <f>IF(ISBLANK(B106),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B106))</f>
         <v/>
@@ -3165,7 +3245,7 @@
       <c r="F106" s="17"/>
       <c r="G106" s="17"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7">
       <c r="A107" s="18" t="str">
         <f>IF(ISBLANK(B107),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B107))</f>
         <v/>
@@ -3177,7 +3257,7 @@
       <c r="F107" s="20"/>
       <c r="G107" s="20"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7">
       <c r="A108" s="8" t="str">
         <f>IF(ISBLANK(B108),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B108))</f>
         <v/>
@@ -3188,7 +3268,7 @@
       <c r="F108" s="17"/>
       <c r="G108" s="17"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7">
       <c r="A109" s="18" t="str">
         <f>IF(ISBLANK(B109),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B109))</f>
         <v/>
@@ -3200,7 +3280,7 @@
       <c r="F109" s="20"/>
       <c r="G109" s="20"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110" s="8" t="str">
         <f>IF(ISBLANK(B110),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B110))</f>
         <v/>
@@ -3211,7 +3291,7 @@
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111" s="18" t="str">
         <f>IF(ISBLANK(B111),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B111))</f>
         <v/>
@@ -3223,7 +3303,7 @@
       <c r="F111" s="20"/>
       <c r="G111" s="20"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112" s="8" t="str">
         <f>IF(ISBLANK(B112),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B112))</f>
         <v/>
@@ -3234,7 +3314,7 @@
       <c r="F112" s="17"/>
       <c r="G112" s="17"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113" s="18" t="str">
         <f>IF(ISBLANK(B113),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B113))</f>
         <v/>
@@ -3246,7 +3326,7 @@
       <c r="F113" s="20"/>
       <c r="G113" s="20"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="8" t="str">
         <f>IF(ISBLANK(B114),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B114))</f>
         <v/>
@@ -3257,7 +3337,7 @@
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115" s="18" t="str">
         <f>IF(ISBLANK(B115),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B115))</f>
         <v/>
@@ -3269,7 +3349,7 @@
       <c r="F115" s="20"/>
       <c r="G115" s="20"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="8" t="str">
         <f>IF(ISBLANK(B116),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B116))</f>
         <v/>
@@ -3280,7 +3360,7 @@
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117" s="18" t="str">
         <f>IF(ISBLANK(B117),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B117))</f>
         <v/>
@@ -3292,7 +3372,7 @@
       <c r="F117" s="20"/>
       <c r="G117" s="20"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="8" t="str">
         <f>IF(ISBLANK(B118),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B118))</f>
         <v/>
@@ -3303,7 +3383,7 @@
       <c r="F118" s="17"/>
       <c r="G118" s="17"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119" s="18" t="str">
         <f>IF(ISBLANK(B119),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B119))</f>
         <v/>
@@ -3315,7 +3395,7 @@
       <c r="F119" s="20"/>
       <c r="G119" s="20"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120" s="8" t="str">
         <f>IF(ISBLANK(B120),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B120))</f>
         <v/>
@@ -3326,7 +3406,7 @@
       <c r="F120" s="17"/>
       <c r="G120" s="17"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121" s="18" t="str">
         <f>IF(ISBLANK(B121),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B121))</f>
         <v/>
@@ -3338,7 +3418,7 @@
       <c r="F121" s="20"/>
       <c r="G121" s="20"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="8" t="str">
         <f>IF(ISBLANK(B122),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B122))</f>
         <v/>
@@ -3349,7 +3429,7 @@
       <c r="F122" s="17"/>
       <c r="G122" s="17"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123" s="18" t="str">
         <f>IF(ISBLANK(B123),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B123))</f>
         <v/>
@@ -3361,7 +3441,7 @@
       <c r="F123" s="20"/>
       <c r="G123" s="20"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="8" t="str">
         <f>IF(ISBLANK(B124),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B124))</f>
         <v/>
@@ -3372,7 +3452,7 @@
       <c r="F124" s="17"/>
       <c r="G124" s="17"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="18" t="str">
         <f>IF(ISBLANK(B125),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B125))</f>
         <v/>
@@ -3384,7 +3464,7 @@
       <c r="F125" s="20"/>
       <c r="G125" s="20"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="8" t="str">
         <f>IF(ISBLANK(B126),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B126))</f>
         <v/>
@@ -3395,7 +3475,7 @@
       <c r="F126" s="17"/>
       <c r="G126" s="17"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127" s="18" t="str">
         <f>IF(ISBLANK(B127),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B127))</f>
         <v/>
@@ -3407,7 +3487,7 @@
       <c r="F127" s="20"/>
       <c r="G127" s="20"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7">
       <c r="A128" s="8" t="str">
         <f>IF(ISBLANK(B128),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B128))</f>
         <v/>
@@ -3418,7 +3498,7 @@
       <c r="F128" s="17"/>
       <c r="G128" s="17"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7">
       <c r="A129" s="18" t="str">
         <f>IF(ISBLANK(B129),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B129))</f>
         <v/>
@@ -3430,7 +3510,7 @@
       <c r="F129" s="20"/>
       <c r="G129" s="20"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7">
       <c r="A130" s="8" t="str">
         <f>IF(ISBLANK(B130),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B130))</f>
         <v/>
@@ -3441,7 +3521,7 @@
       <c r="F130" s="17"/>
       <c r="G130" s="17"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7">
       <c r="A131" s="18" t="str">
         <f>IF(ISBLANK(B131),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B131))</f>
         <v/>
@@ -3453,7 +3533,7 @@
       <c r="F131" s="20"/>
       <c r="G131" s="20"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132" s="8" t="str">
         <f>IF(ISBLANK(B132),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B132))</f>
         <v/>
@@ -3464,7 +3544,7 @@
       <c r="F132" s="17"/>
       <c r="G132" s="17"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7">
       <c r="A133" s="18" t="str">
         <f>IF(ISBLANK(B133),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B133))</f>
         <v/>
@@ -3476,7 +3556,7 @@
       <c r="F133" s="20"/>
       <c r="G133" s="20"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7">
       <c r="A134" s="8" t="str">
         <f>IF(ISBLANK(B134),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B134))</f>
         <v/>
@@ -3487,7 +3567,7 @@
       <c r="F134" s="17"/>
       <c r="G134" s="17"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7">
       <c r="A135" s="18" t="str">
         <f>IF(ISBLANK(B135),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B135))</f>
         <v/>
@@ -3499,7 +3579,7 @@
       <c r="F135" s="20"/>
       <c r="G135" s="20"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7">
       <c r="A136" s="8" t="str">
         <f>IF(ISBLANK(B136),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B136))</f>
         <v/>
@@ -3510,7 +3590,7 @@
       <c r="F136" s="17"/>
       <c r="G136" s="17"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7">
       <c r="A137" s="18" t="str">
         <f>IF(ISBLANK(B137),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B137))</f>
         <v/>
@@ -3522,7 +3602,7 @@
       <c r="F137" s="20"/>
       <c r="G137" s="20"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7">
       <c r="A138" s="8" t="str">
         <f>IF(ISBLANK(B138),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B138))</f>
         <v/>
@@ -3533,7 +3613,7 @@
       <c r="F138" s="17"/>
       <c r="G138" s="17"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7">
       <c r="A139" s="18" t="str">
         <f>IF(ISBLANK(B139),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B139))</f>
         <v/>
@@ -3545,7 +3625,7 @@
       <c r="F139" s="20"/>
       <c r="G139" s="20"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7">
       <c r="A140" s="8" t="str">
         <f>IF(ISBLANK(B140),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B140))</f>
         <v/>
@@ -3556,7 +3636,7 @@
       <c r="F140" s="17"/>
       <c r="G140" s="17"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7">
       <c r="A141" s="18" t="str">
         <f>IF(ISBLANK(B141),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B141))</f>
         <v/>
@@ -3568,7 +3648,7 @@
       <c r="F141" s="20"/>
       <c r="G141" s="20"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7">
       <c r="A142" s="8" t="str">
         <f>IF(ISBLANK(B142),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B142))</f>
         <v/>
@@ -3579,7 +3659,7 @@
       <c r="F142" s="17"/>
       <c r="G142" s="17"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143" s="18" t="str">
         <f>IF(ISBLANK(B143),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B143))</f>
         <v/>
@@ -3591,7 +3671,7 @@
       <c r="F143" s="20"/>
       <c r="G143" s="20"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144" s="8" t="str">
         <f>IF(ISBLANK(B144),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B144))</f>
         <v/>
@@ -3602,7 +3682,7 @@
       <c r="F144" s="17"/>
       <c r="G144" s="17"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7">
       <c r="A145" s="18" t="str">
         <f>IF(ISBLANK(B145),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B145))</f>
         <v/>
@@ -3614,7 +3694,7 @@
       <c r="F145" s="20"/>
       <c r="G145" s="20"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7">
       <c r="A146" s="8" t="str">
         <f>IF(ISBLANK(B146),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B146))</f>
         <v/>
@@ -3625,7 +3705,7 @@
       <c r="F146" s="17"/>
       <c r="G146" s="17"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7">
       <c r="A147" s="18" t="str">
         <f>IF(ISBLANK(B147),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B147))</f>
         <v/>
@@ -3637,7 +3717,7 @@
       <c r="F147" s="20"/>
       <c r="G147" s="20"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7">
       <c r="A148" s="8" t="str">
         <f>IF(ISBLANK(B148),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B148))</f>
         <v/>
@@ -3648,7 +3728,7 @@
       <c r="F148" s="17"/>
       <c r="G148" s="17"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7">
       <c r="A149" s="18" t="str">
         <f>IF(ISBLANK(B149),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B149))</f>
         <v/>
@@ -3660,7 +3740,7 @@
       <c r="F149" s="20"/>
       <c r="G149" s="20"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7">
       <c r="A150" s="8" t="str">
         <f>IF(ISBLANK(B150),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B150))</f>
         <v/>
@@ -3671,7 +3751,7 @@
       <c r="F150" s="17"/>
       <c r="G150" s="17"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7">
       <c r="A151" s="18" t="str">
         <f>IF(ISBLANK(B151),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B151))</f>
         <v/>
@@ -3683,7 +3763,7 @@
       <c r="F151" s="20"/>
       <c r="G151" s="20"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7">
       <c r="A152" s="8" t="str">
         <f>IF(ISBLANK(B152),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B152))</f>
         <v/>
@@ -3694,7 +3774,7 @@
       <c r="F152" s="17"/>
       <c r="G152" s="17"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7">
       <c r="A153" s="18" t="str">
         <f>IF(ISBLANK(B153),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B153))</f>
         <v/>
@@ -3706,7 +3786,7 @@
       <c r="F153" s="20"/>
       <c r="G153" s="20"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7">
       <c r="A154" s="8" t="str">
         <f>IF(ISBLANK(B154),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B154))</f>
         <v/>
@@ -3717,7 +3797,7 @@
       <c r="F154" s="17"/>
       <c r="G154" s="17"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7">
       <c r="A155" s="18" t="str">
         <f>IF(ISBLANK(B155),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B155))</f>
         <v/>
@@ -3729,7 +3809,7 @@
       <c r="F155" s="20"/>
       <c r="G155" s="20"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7">
       <c r="A156" s="8" t="str">
         <f>IF(ISBLANK(B156),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B156))</f>
         <v/>
@@ -3740,7 +3820,7 @@
       <c r="F156" s="17"/>
       <c r="G156" s="17"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7">
       <c r="A157" s="18" t="str">
         <f>IF(ISBLANK(B157),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B157))</f>
         <v/>
@@ -3752,7 +3832,7 @@
       <c r="F157" s="20"/>
       <c r="G157" s="20"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7">
       <c r="A158" s="8" t="str">
         <f>IF(ISBLANK(B158),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B158))</f>
         <v/>
@@ -3763,7 +3843,7 @@
       <c r="F158" s="17"/>
       <c r="G158" s="17"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7">
       <c r="A159" s="18" t="str">
         <f>IF(ISBLANK(B159),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B159))</f>
         <v/>
@@ -3775,7 +3855,7 @@
       <c r="F159" s="20"/>
       <c r="G159" s="20"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7">
       <c r="A160" s="8" t="str">
         <f>IF(ISBLANK(B160),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B160))</f>
         <v/>
@@ -3786,7 +3866,7 @@
       <c r="F160" s="17"/>
       <c r="G160" s="17"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7">
       <c r="A161" s="18" t="str">
         <f>IF(ISBLANK(B161),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B161))</f>
         <v/>
@@ -3798,7 +3878,7 @@
       <c r="F161" s="20"/>
       <c r="G161" s="20"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7">
       <c r="A162" s="8" t="str">
         <f>IF(ISBLANK(B162),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B162))</f>
         <v/>
@@ -3809,7 +3889,7 @@
       <c r="F162" s="17"/>
       <c r="G162" s="17"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7">
       <c r="A163" s="18" t="str">
         <f>IF(ISBLANK(B163),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B163))</f>
         <v/>
@@ -3821,7 +3901,7 @@
       <c r="F163" s="20"/>
       <c r="G163" s="20"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7">
       <c r="A164" s="8" t="str">
         <f>IF(ISBLANK(B164),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B164))</f>
         <v/>
@@ -3832,7 +3912,7 @@
       <c r="F164" s="17"/>
       <c r="G164" s="17"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7">
       <c r="A165" s="18" t="str">
         <f>IF(ISBLANK(B165),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B165))</f>
         <v/>
@@ -3844,7 +3924,7 @@
       <c r="F165" s="20"/>
       <c r="G165" s="20"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7">
       <c r="A166" s="8" t="str">
         <f>IF(ISBLANK(B166),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B166))</f>
         <v/>
@@ -3855,7 +3935,7 @@
       <c r="F166" s="17"/>
       <c r="G166" s="17"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7">
       <c r="A167" s="18" t="str">
         <f>IF(ISBLANK(B167),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B167))</f>
         <v/>
@@ -3867,7 +3947,7 @@
       <c r="F167" s="20"/>
       <c r="G167" s="20"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7">
       <c r="A168" s="8" t="str">
         <f>IF(ISBLANK(B168),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B168))</f>
         <v/>
@@ -3878,7 +3958,7 @@
       <c r="F168" s="17"/>
       <c r="G168" s="17"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7">
       <c r="A169" s="18" t="str">
         <f>IF(ISBLANK(B169),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B169))</f>
         <v/>
@@ -3890,7 +3970,7 @@
       <c r="F169" s="20"/>
       <c r="G169" s="20"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7">
       <c r="A170" s="8" t="str">
         <f>IF(ISBLANK(B170),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B170))</f>
         <v/>
@@ -3901,7 +3981,7 @@
       <c r="F170" s="17"/>
       <c r="G170" s="17"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7">
       <c r="A171" s="18" t="str">
         <f>IF(ISBLANK(B171),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B171))</f>
         <v/>
@@ -3913,7 +3993,7 @@
       <c r="F171" s="20"/>
       <c r="G171" s="20"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7">
       <c r="A172" s="8" t="str">
         <f>IF(ISBLANK(B172),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B172))</f>
         <v/>
@@ -3924,7 +4004,7 @@
       <c r="F172" s="17"/>
       <c r="G172" s="17"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7">
       <c r="A173" s="18" t="str">
         <f>IF(ISBLANK(B173),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B173))</f>
         <v/>
@@ -3936,7 +4016,7 @@
       <c r="F173" s="20"/>
       <c r="G173" s="20"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7">
       <c r="A174" s="8" t="str">
         <f>IF(ISBLANK(B174),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B174))</f>
         <v/>
@@ -3947,7 +4027,7 @@
       <c r="F174" s="17"/>
       <c r="G174" s="17"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7">
       <c r="A175" s="18" t="str">
         <f>IF(ISBLANK(B175),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B175))</f>
         <v/>
@@ -3959,7 +4039,7 @@
       <c r="F175" s="20"/>
       <c r="G175" s="20"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7">
       <c r="A176" s="8" t="str">
         <f>IF(ISBLANK(B176),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B176))</f>
         <v/>
@@ -3970,7 +4050,7 @@
       <c r="F176" s="17"/>
       <c r="G176" s="17"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7">
       <c r="A177" s="18" t="str">
         <f>IF(ISBLANK(B177),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B177))</f>
         <v/>
@@ -3982,7 +4062,7 @@
       <c r="F177" s="20"/>
       <c r="G177" s="20"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7">
       <c r="A178" s="8" t="str">
         <f>IF(ISBLANK(B178),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B178))</f>
         <v/>
@@ -3993,7 +4073,7 @@
       <c r="F178" s="17"/>
       <c r="G178" s="17"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7">
       <c r="A179" s="18" t="str">
         <f>IF(ISBLANK(B179),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B179))</f>
         <v/>
@@ -4005,7 +4085,7 @@
       <c r="F179" s="20"/>
       <c r="G179" s="20"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7">
       <c r="A180" s="8" t="str">
         <f>IF(ISBLANK(B180),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B180))</f>
         <v/>
@@ -4016,7 +4096,7 @@
       <c r="F180" s="17"/>
       <c r="G180" s="17"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7">
       <c r="A181" s="18" t="str">
         <f>IF(ISBLANK(B181),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B181))</f>
         <v/>
@@ -4028,7 +4108,7 @@
       <c r="F181" s="20"/>
       <c r="G181" s="20"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7">
       <c r="A182" s="8" t="str">
         <f>IF(ISBLANK(B182),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B182))</f>
         <v/>
@@ -4039,7 +4119,7 @@
       <c r="F182" s="17"/>
       <c r="G182" s="17"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7">
       <c r="A183" s="18" t="str">
         <f>IF(ISBLANK(B183),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B183))</f>
         <v/>
@@ -4051,7 +4131,7 @@
       <c r="F183" s="20"/>
       <c r="G183" s="20"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7">
       <c r="A184" s="8" t="str">
         <f>IF(ISBLANK(B184),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B184))</f>
         <v/>
@@ -4062,7 +4142,7 @@
       <c r="F184" s="17"/>
       <c r="G184" s="17"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7">
       <c r="A185" s="18" t="str">
         <f>IF(ISBLANK(B185),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B185))</f>
         <v/>
@@ -4074,7 +4154,7 @@
       <c r="F185" s="20"/>
       <c r="G185" s="20"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7">
       <c r="A186" s="8" t="str">
         <f>IF(ISBLANK(B186),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B186))</f>
         <v/>
@@ -4085,7 +4165,7 @@
       <c r="F186" s="17"/>
       <c r="G186" s="17"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7">
       <c r="A187" s="18" t="str">
         <f>IF(ISBLANK(B187),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B187))</f>
         <v/>
@@ -4097,7 +4177,7 @@
       <c r="F187" s="20"/>
       <c r="G187" s="20"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7">
       <c r="A188" s="8" t="str">
         <f>IF(ISBLANK(B188),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B188))</f>
         <v/>
@@ -4108,7 +4188,7 @@
       <c r="F188" s="17"/>
       <c r="G188" s="17"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7">
       <c r="A189" s="18" t="str">
         <f>IF(ISBLANK(B189),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B189))</f>
         <v/>
@@ -4120,7 +4200,7 @@
       <c r="F189" s="20"/>
       <c r="G189" s="20"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7">
       <c r="A190" s="8" t="str">
         <f>IF(ISBLANK(B190),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B190))</f>
         <v/>
@@ -4131,7 +4211,7 @@
       <c r="F190" s="17"/>
       <c r="G190" s="17"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7">
       <c r="A191" s="18" t="str">
         <f>IF(ISBLANK(B191),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B191))</f>
         <v/>
@@ -4143,7 +4223,7 @@
       <c r="F191" s="20"/>
       <c r="G191" s="20"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7">
       <c r="A192" s="8" t="str">
         <f>IF(ISBLANK(B192),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B192))</f>
         <v/>
@@ -4154,7 +4234,7 @@
       <c r="F192" s="17"/>
       <c r="G192" s="17"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7">
       <c r="A193" s="18" t="str">
         <f>IF(ISBLANK(B193),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B193))</f>
         <v/>
@@ -4166,7 +4246,7 @@
       <c r="F193" s="20"/>
       <c r="G193" s="20"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7">
       <c r="A194" s="8" t="str">
         <f>IF(ISBLANK(B194),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B194))</f>
         <v/>
@@ -4177,7 +4257,7 @@
       <c r="F194" s="17"/>
       <c r="G194" s="17"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7">
       <c r="A195" s="18" t="str">
         <f>IF(ISBLANK(B195),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B195))</f>
         <v/>
@@ -4189,7 +4269,7 @@
       <c r="F195" s="20"/>
       <c r="G195" s="20"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7">
       <c r="A196" s="8" t="str">
         <f>IF(ISBLANK(B196),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B196))</f>
         <v/>
@@ -4200,7 +4280,7 @@
       <c r="F196" s="17"/>
       <c r="G196" s="17"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7">
       <c r="A197" s="18" t="str">
         <f>IF(ISBLANK(B197),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B197))</f>
         <v/>
@@ -4212,7 +4292,7 @@
       <c r="F197" s="20"/>
       <c r="G197" s="20"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7">
       <c r="A198" s="8" t="str">
         <f>IF(ISBLANK(B198),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B198))</f>
         <v/>
@@ -4223,7 +4303,7 @@
       <c r="F198" s="17"/>
       <c r="G198" s="17"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7">
       <c r="A199" s="18" t="str">
         <f>IF(ISBLANK(B199),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B199))</f>
         <v/>
@@ -4235,7 +4315,7 @@
       <c r="F199" s="20"/>
       <c r="G199" s="20"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7">
       <c r="A200" s="8" t="str">
         <f>IF(ISBLANK(B200),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B200))</f>
         <v/>
@@ -4246,7 +4326,7 @@
       <c r="F200" s="17"/>
       <c r="G200" s="17"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7">
       <c r="A201" s="18" t="str">
         <f>IF(ISBLANK(B201),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B201))</f>
         <v/>
@@ -4258,7 +4338,7 @@
       <c r="F201" s="20"/>
       <c r="G201" s="20"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7">
       <c r="A202" s="8" t="str">
         <f>IF(ISBLANK(B202),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B202))</f>
         <v/>
@@ -4269,7 +4349,7 @@
       <c r="F202" s="17"/>
       <c r="G202" s="17"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7">
       <c r="A203" s="18" t="str">
         <f>IF(ISBLANK(B203),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B203))</f>
         <v/>
@@ -4281,7 +4361,7 @@
       <c r="F203" s="20"/>
       <c r="G203" s="20"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7">
       <c r="A204" s="8" t="str">
         <f>IF(ISBLANK(B204),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B204))</f>
         <v/>
@@ -4292,7 +4372,7 @@
       <c r="F204" s="17"/>
       <c r="G204" s="17"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7">
       <c r="A205" s="18" t="str">
         <f>IF(ISBLANK(B205),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B205))</f>
         <v/>
@@ -4304,7 +4384,7 @@
       <c r="F205" s="20"/>
       <c r="G205" s="20"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7">
       <c r="A206" s="8" t="str">
         <f>IF(ISBLANK(B206),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B206))</f>
         <v/>
@@ -4315,7 +4395,7 @@
       <c r="F206" s="17"/>
       <c r="G206" s="17"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7">
       <c r="A207" s="18" t="str">
         <f>IF(ISBLANK(B207),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B207))</f>
         <v/>
@@ -4327,7 +4407,7 @@
       <c r="F207" s="20"/>
       <c r="G207" s="20"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7">
       <c r="A208" s="8" t="str">
         <f>IF(ISBLANK(B208),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B208))</f>
         <v/>
@@ -4338,7 +4418,7 @@
       <c r="F208" s="17"/>
       <c r="G208" s="17"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7">
       <c r="A209" s="18" t="str">
         <f>IF(ISBLANK(B209),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B209))</f>
         <v/>
@@ -4350,7 +4430,7 @@
       <c r="F209" s="20"/>
       <c r="G209" s="20"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7">
       <c r="A210" s="8" t="str">
         <f>IF(ISBLANK(B210),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B210))</f>
         <v/>
@@ -4361,7 +4441,7 @@
       <c r="F210" s="17"/>
       <c r="G210" s="17"/>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7">
       <c r="A211" s="18" t="str">
         <f>IF(ISBLANK(B211),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B211))</f>
         <v/>
@@ -4373,7 +4453,7 @@
       <c r="F211" s="20"/>
       <c r="G211" s="20"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7">
       <c r="A212" s="8" t="str">
         <f>IF(ISBLANK(B212),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B212))</f>
         <v/>
@@ -4384,7 +4464,7 @@
       <c r="F212" s="17"/>
       <c r="G212" s="17"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7">
       <c r="A213" s="18" t="str">
         <f>IF(ISBLANK(B213),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B213))</f>
         <v/>
@@ -4396,7 +4476,7 @@
       <c r="F213" s="20"/>
       <c r="G213" s="20"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7">
       <c r="A214" s="8" t="str">
         <f>IF(ISBLANK(B214),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B214))</f>
         <v/>
@@ -4407,7 +4487,7 @@
       <c r="F214" s="17"/>
       <c r="G214" s="17"/>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7">
       <c r="A215" s="18" t="str">
         <f>IF(ISBLANK(B215),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B215))</f>
         <v/>
@@ -4419,7 +4499,7 @@
       <c r="F215" s="20"/>
       <c r="G215" s="20"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7">
       <c r="A216" s="8" t="str">
         <f>IF(ISBLANK(B216),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B216))</f>
         <v/>
@@ -4430,7 +4510,7 @@
       <c r="F216" s="17"/>
       <c r="G216" s="17"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7">
       <c r="A217" s="18" t="str">
         <f>IF(ISBLANK(B217),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B217))</f>
         <v/>
@@ -4442,7 +4522,7 @@
       <c r="F217" s="20"/>
       <c r="G217" s="20"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7">
       <c r="A218" s="8" t="str">
         <f>IF(ISBLANK(B218),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B218))</f>
         <v/>
@@ -4453,7 +4533,7 @@
       <c r="F218" s="17"/>
       <c r="G218" s="17"/>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7">
       <c r="A219" s="18" t="str">
         <f>IF(ISBLANK(B219),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B219))</f>
         <v/>
@@ -4465,7 +4545,7 @@
       <c r="F219" s="20"/>
       <c r="G219" s="20"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7">
       <c r="A220" s="8" t="str">
         <f>IF(ISBLANK(B220),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B220))</f>
         <v/>
@@ -4476,7 +4556,7 @@
       <c r="F220" s="17"/>
       <c r="G220" s="17"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7">
       <c r="A221" s="18" t="str">
         <f>IF(ISBLANK(B221),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B221))</f>
         <v/>
@@ -4488,7 +4568,7 @@
       <c r="F221" s="20"/>
       <c r="G221" s="20"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7">
       <c r="A222" s="8" t="str">
         <f>IF(ISBLANK(B222),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B222))</f>
         <v/>
@@ -4499,7 +4579,7 @@
       <c r="F222" s="17"/>
       <c r="G222" s="17"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7">
       <c r="A223" s="18" t="str">
         <f>IF(ISBLANK(B223),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B223))</f>
         <v/>
@@ -4511,7 +4591,7 @@
       <c r="F223" s="20"/>
       <c r="G223" s="20"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7">
       <c r="A224" s="8" t="str">
         <f>IF(ISBLANK(B224),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B224))</f>
         <v/>
@@ -4522,7 +4602,7 @@
       <c r="F224" s="17"/>
       <c r="G224" s="17"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7">
       <c r="A225" s="18" t="str">
         <f>IF(ISBLANK(B225),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B225))</f>
         <v/>
@@ -4534,7 +4614,7 @@
       <c r="F225" s="20"/>
       <c r="G225" s="20"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7">
       <c r="A226" s="8" t="str">
         <f>IF(ISBLANK(B226),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B226))</f>
         <v/>
@@ -4545,7 +4625,7 @@
       <c r="F226" s="17"/>
       <c r="G226" s="17"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7">
       <c r="A227" s="18" t="str">
         <f>IF(ISBLANK(B227),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B227))</f>
         <v/>
@@ -4557,7 +4637,7 @@
       <c r="F227" s="20"/>
       <c r="G227" s="20"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7">
       <c r="A228" s="8" t="str">
         <f>IF(ISBLANK(B228),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B228))</f>
         <v/>
@@ -4568,7 +4648,7 @@
       <c r="F228" s="17"/>
       <c r="G228" s="17"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7">
       <c r="A229" s="18" t="str">
         <f>IF(ISBLANK(B229),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B229))</f>
         <v/>
@@ -4580,7 +4660,7 @@
       <c r="F229" s="20"/>
       <c r="G229" s="20"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7">
       <c r="A230" s="8" t="str">
         <f>IF(ISBLANK(B230),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B230))</f>
         <v/>
@@ -4591,7 +4671,7 @@
       <c r="F230" s="17"/>
       <c r="G230" s="17"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7">
       <c r="A231" s="18" t="str">
         <f>IF(ISBLANK(B231),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B231))</f>
         <v/>
@@ -4603,7 +4683,7 @@
       <c r="F231" s="20"/>
       <c r="G231" s="20"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7">
       <c r="A232" s="8" t="str">
         <f>IF(ISBLANK(B232),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B232))</f>
         <v/>
@@ -4614,7 +4694,7 @@
       <c r="F232" s="17"/>
       <c r="G232" s="17"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7">
       <c r="A233" s="18" t="str">
         <f>IF(ISBLANK(B233),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B233))</f>
         <v/>
@@ -4626,7 +4706,7 @@
       <c r="F233" s="20"/>
       <c r="G233" s="20"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7">
       <c r="A234" s="8" t="str">
         <f>IF(ISBLANK(B234),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B234))</f>
         <v/>
@@ -4637,7 +4717,7 @@
       <c r="F234" s="17"/>
       <c r="G234" s="17"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7">
       <c r="A235" s="18" t="str">
         <f>IF(ISBLANK(B235),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B235))</f>
         <v/>
@@ -4649,7 +4729,7 @@
       <c r="F235" s="20"/>
       <c r="G235" s="20"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7">
       <c r="A236" s="8" t="str">
         <f>IF(ISBLANK(B236),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B236))</f>
         <v/>
@@ -4660,7 +4740,7 @@
       <c r="F236" s="17"/>
       <c r="G236" s="17"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7">
       <c r="A237" s="18" t="str">
         <f>IF(ISBLANK(B237),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B237))</f>
         <v/>
@@ -4672,7 +4752,7 @@
       <c r="F237" s="20"/>
       <c r="G237" s="20"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7">
       <c r="A238" s="8" t="str">
         <f>IF(ISBLANK(B238),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B238))</f>
         <v/>
@@ -4683,7 +4763,7 @@
       <c r="F238" s="17"/>
       <c r="G238" s="17"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7">
       <c r="A239" s="18" t="str">
         <f>IF(ISBLANK(B239),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B239))</f>
         <v/>
@@ -4695,7 +4775,7 @@
       <c r="F239" s="20"/>
       <c r="G239" s="20"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7">
       <c r="A240" s="8" t="str">
         <f>IF(ISBLANK(B240),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B240))</f>
         <v/>
@@ -4706,7 +4786,7 @@
       <c r="F240" s="17"/>
       <c r="G240" s="17"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7">
       <c r="A241" s="18" t="str">
         <f>IF(ISBLANK(B241),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B241))</f>
         <v/>
@@ -4718,7 +4798,7 @@
       <c r="F241" s="20"/>
       <c r="G241" s="20"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7">
       <c r="A242" s="8" t="str">
         <f>IF(ISBLANK(B242),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B242))</f>
         <v/>
@@ -4729,7 +4809,7 @@
       <c r="F242" s="17"/>
       <c r="G242" s="17"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7">
       <c r="A243" s="18" t="str">
         <f>IF(ISBLANK(B243),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B243))</f>
         <v/>
@@ -4741,7 +4821,7 @@
       <c r="F243" s="20"/>
       <c r="G243" s="20"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7">
       <c r="A244" s="8" t="str">
         <f>IF(ISBLANK(B244),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B244))</f>
         <v/>
@@ -4752,7 +4832,7 @@
       <c r="F244" s="17"/>
       <c r="G244" s="17"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7">
       <c r="A245" s="18" t="str">
         <f>IF(ISBLANK(B245),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B245))</f>
         <v/>
@@ -4764,7 +4844,7 @@
       <c r="F245" s="20"/>
       <c r="G245" s="20"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7">
       <c r="A246" s="8" t="str">
         <f>IF(ISBLANK(B246),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B246))</f>
         <v/>
@@ -4775,7 +4855,7 @@
       <c r="F246" s="17"/>
       <c r="G246" s="17"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7">
       <c r="A247" s="18" t="str">
         <f>IF(ISBLANK(B247),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B247))</f>
         <v/>
@@ -4787,7 +4867,7 @@
       <c r="F247" s="20"/>
       <c r="G247" s="20"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7">
       <c r="A248" s="8" t="str">
         <f>IF(ISBLANK(B248),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B248))</f>
         <v/>
@@ -4798,7 +4878,7 @@
       <c r="F248" s="17"/>
       <c r="G248" s="17"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7">
       <c r="A249" s="18" t="str">
         <f>IF(ISBLANK(B249),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B249))</f>
         <v/>
@@ -4810,7 +4890,7 @@
       <c r="F249" s="20"/>
       <c r="G249" s="20"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7">
       <c r="A250" s="8" t="str">
         <f>IF(ISBLANK(B250),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B250))</f>
         <v/>
@@ -4821,7 +4901,7 @@
       <c r="F250" s="17"/>
       <c r="G250" s="17"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7">
       <c r="A251" s="18" t="str">
         <f>IF(ISBLANK(B251),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B251))</f>
         <v/>
@@ -4833,7 +4913,7 @@
       <c r="F251" s="20"/>
       <c r="G251" s="20"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7">
       <c r="A252" s="8" t="str">
         <f>IF(ISBLANK(B252),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B252))</f>
         <v/>
@@ -4844,7 +4924,7 @@
       <c r="F252" s="17"/>
       <c r="G252" s="17"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7">
       <c r="A253" s="18" t="str">
         <f>IF(ISBLANK(B253),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B253))</f>
         <v/>
@@ -4856,7 +4936,7 @@
       <c r="F253" s="20"/>
       <c r="G253" s="20"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7">
       <c r="A254" s="8" t="str">
         <f>IF(ISBLANK(B254),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B254))</f>
         <v/>
@@ -4867,7 +4947,7 @@
       <c r="F254" s="17"/>
       <c r="G254" s="17"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7">
       <c r="A255" s="18" t="str">
         <f>IF(ISBLANK(B255),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B255))</f>
         <v/>
@@ -4879,7 +4959,7 @@
       <c r="F255" s="20"/>
       <c r="G255" s="20"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7">
       <c r="A256" s="8" t="str">
         <f>IF(ISBLANK(B256),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B256))</f>
         <v/>
@@ -4890,7 +4970,7 @@
       <c r="F256" s="17"/>
       <c r="G256" s="17"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7">
       <c r="A257" s="18" t="str">
         <f>IF(ISBLANK(B257),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B257))</f>
         <v/>
@@ -4902,7 +4982,7 @@
       <c r="F257" s="20"/>
       <c r="G257" s="20"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7">
       <c r="A258" s="8" t="str">
         <f>IF(ISBLANK(B258),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B258))</f>
         <v/>
@@ -4913,7 +4993,7 @@
       <c r="F258" s="17"/>
       <c r="G258" s="17"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7">
       <c r="A259" s="18" t="str">
         <f>IF(ISBLANK(B259),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B259))</f>
         <v/>
@@ -4925,7 +5005,7 @@
       <c r="F259" s="20"/>
       <c r="G259" s="20"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7">
       <c r="A260" s="8" t="str">
         <f>IF(ISBLANK(B260),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B260))</f>
         <v/>
@@ -4936,7 +5016,7 @@
       <c r="F260" s="17"/>
       <c r="G260" s="17"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7">
       <c r="A261" s="18" t="str">
         <f>IF(ISBLANK(B261),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B261))</f>
         <v/>
@@ -4948,7 +5028,7 @@
       <c r="F261" s="20"/>
       <c r="G261" s="20"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7">
       <c r="A262" s="8" t="str">
         <f>IF(ISBLANK(B262),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B262))</f>
         <v/>
@@ -4959,7 +5039,7 @@
       <c r="F262" s="17"/>
       <c r="G262" s="17"/>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7">
       <c r="A263" s="18" t="str">
         <f>IF(ISBLANK(B263),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B263))</f>
         <v/>
@@ -4971,7 +5051,7 @@
       <c r="F263" s="20"/>
       <c r="G263" s="20"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7">
       <c r="A264" s="8" t="str">
         <f>IF(ISBLANK(B264),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B264))</f>
         <v/>
@@ -4982,7 +5062,7 @@
       <c r="F264" s="17"/>
       <c r="G264" s="17"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7">
       <c r="A265" s="18" t="str">
         <f>IF(ISBLANK(B265),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B265))</f>
         <v/>
@@ -4994,7 +5074,7 @@
       <c r="F265" s="20"/>
       <c r="G265" s="20"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7">
       <c r="A266" s="8" t="str">
         <f>IF(ISBLANK(B266),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B266))</f>
         <v/>
@@ -5005,7 +5085,7 @@
       <c r="F266" s="17"/>
       <c r="G266" s="17"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7">
       <c r="A267" s="18" t="str">
         <f>IF(ISBLANK(B267),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B267))</f>
         <v/>
@@ -5017,7 +5097,7 @@
       <c r="F267" s="20"/>
       <c r="G267" s="20"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7">
       <c r="A268" s="8" t="str">
         <f>IF(ISBLANK(B268),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B268))</f>
         <v/>
@@ -5028,7 +5108,7 @@
       <c r="F268" s="17"/>
       <c r="G268" s="17"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7">
       <c r="A269" s="18" t="str">
         <f>IF(ISBLANK(B269),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B269))</f>
         <v/>
@@ -5040,7 +5120,7 @@
       <c r="F269" s="20"/>
       <c r="G269" s="20"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7">
       <c r="A270" s="8" t="str">
         <f>IF(ISBLANK(B270),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B270))</f>
         <v/>
@@ -5051,7 +5131,7 @@
       <c r="F270" s="17"/>
       <c r="G270" s="17"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7">
       <c r="A271" s="18" t="str">
         <f>IF(ISBLANK(B271),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B271))</f>
         <v/>
@@ -5063,7 +5143,7 @@
       <c r="F271" s="20"/>
       <c r="G271" s="20"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7">
       <c r="A272" s="8" t="str">
         <f>IF(ISBLANK(B272),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B272))</f>
         <v/>
@@ -5074,7 +5154,7 @@
       <c r="F272" s="17"/>
       <c r="G272" s="17"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7">
       <c r="A273" s="18" t="str">
         <f>IF(ISBLANK(B273),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B273))</f>
         <v/>
@@ -5086,7 +5166,7 @@
       <c r="F273" s="20"/>
       <c r="G273" s="20"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7">
       <c r="A274" s="8" t="str">
         <f>IF(ISBLANK(B274),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B274))</f>
         <v/>
@@ -5097,7 +5177,7 @@
       <c r="F274" s="17"/>
       <c r="G274" s="17"/>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7">
       <c r="A275" s="18" t="str">
         <f>IF(ISBLANK(B275),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B275))</f>
         <v/>
@@ -5109,7 +5189,7 @@
       <c r="F275" s="20"/>
       <c r="G275" s="20"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7">
       <c r="A276" s="8" t="str">
         <f>IF(ISBLANK(B276),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B276))</f>
         <v/>
@@ -5120,7 +5200,7 @@
       <c r="F276" s="17"/>
       <c r="G276" s="17"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7">
       <c r="A277" s="18" t="str">
         <f>IF(ISBLANK(B277),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B277))</f>
         <v/>
@@ -5132,7 +5212,7 @@
       <c r="F277" s="20"/>
       <c r="G277" s="20"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7">
       <c r="A278" s="8" t="str">
         <f>IF(ISBLANK(B278),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B278))</f>
         <v/>
@@ -5143,7 +5223,7 @@
       <c r="F278" s="17"/>
       <c r="G278" s="17"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7">
       <c r="A279" s="18" t="str">
         <f>IF(ISBLANK(B279),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B279))</f>
         <v/>
@@ -5155,7 +5235,7 @@
       <c r="F279" s="20"/>
       <c r="G279" s="20"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7">
       <c r="A280" s="8" t="str">
         <f>IF(ISBLANK(B280),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B280))</f>
         <v/>
@@ -5166,7 +5246,7 @@
       <c r="F280" s="17"/>
       <c r="G280" s="17"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7">
       <c r="A281" s="18" t="str">
         <f>IF(ISBLANK(B281),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B281))</f>
         <v/>
@@ -5178,7 +5258,7 @@
       <c r="F281" s="20"/>
       <c r="G281" s="20"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7">
       <c r="A282" s="8" t="str">
         <f>IF(ISBLANK(B282),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B282))</f>
         <v/>
@@ -5189,7 +5269,7 @@
       <c r="F282" s="17"/>
       <c r="G282" s="17"/>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7">
       <c r="A283" s="18" t="str">
         <f>IF(ISBLANK(B283),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B283))</f>
         <v/>
@@ -5201,7 +5281,7 @@
       <c r="F283" s="20"/>
       <c r="G283" s="20"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7">
       <c r="A284" s="8" t="str">
         <f>IF(ISBLANK(B284),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B284))</f>
         <v/>
@@ -5212,7 +5292,7 @@
       <c r="F284" s="17"/>
       <c r="G284" s="17"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7">
       <c r="A285" s="18" t="str">
         <f>IF(ISBLANK(B285),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B285))</f>
         <v/>
@@ -5224,7 +5304,7 @@
       <c r="F285" s="20"/>
       <c r="G285" s="20"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7">
       <c r="A286" s="8" t="str">
         <f>IF(ISBLANK(B286),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B286))</f>
         <v/>
@@ -5235,7 +5315,7 @@
       <c r="F286" s="17"/>
       <c r="G286" s="17"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7">
       <c r="A287" s="18" t="str">
         <f>IF(ISBLANK(B287),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B287))</f>
         <v/>
@@ -5247,7 +5327,7 @@
       <c r="F287" s="20"/>
       <c r="G287" s="20"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7">
       <c r="A288" s="8" t="str">
         <f>IF(ISBLANK(B288),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B288))</f>
         <v/>
@@ -5258,7 +5338,7 @@
       <c r="F288" s="17"/>
       <c r="G288" s="17"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7">
       <c r="A289" s="18" t="str">
         <f>IF(ISBLANK(B289),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B289))</f>
         <v/>
@@ -5270,7 +5350,7 @@
       <c r="F289" s="20"/>
       <c r="G289" s="20"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7">
       <c r="A290" s="8" t="str">
         <f>IF(ISBLANK(B290),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B290))</f>
         <v/>
@@ -5281,7 +5361,7 @@
       <c r="F290" s="17"/>
       <c r="G290" s="17"/>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7">
       <c r="A291" s="18" t="str">
         <f>IF(ISBLANK(B291),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B291))</f>
         <v/>
@@ -5293,7 +5373,7 @@
       <c r="F291" s="20"/>
       <c r="G291" s="20"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7">
       <c r="A292" s="8" t="str">
         <f>IF(ISBLANK(B292),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B292))</f>
         <v/>
@@ -5304,7 +5384,7 @@
       <c r="F292" s="17"/>
       <c r="G292" s="17"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7">
       <c r="A293" s="18" t="str">
         <f>IF(ISBLANK(B293),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B293))</f>
         <v/>
@@ -5316,7 +5396,7 @@
       <c r="F293" s="20"/>
       <c r="G293" s="20"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7">
       <c r="A294" s="8" t="str">
         <f>IF(ISBLANK(B294),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B294))</f>
         <v/>
@@ -5327,7 +5407,7 @@
       <c r="F294" s="17"/>
       <c r="G294" s="17"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7">
       <c r="A295" s="18" t="str">
         <f>IF(ISBLANK(B295),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B295))</f>
         <v/>
@@ -5339,7 +5419,7 @@
       <c r="F295" s="20"/>
       <c r="G295" s="20"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7">
       <c r="A296" s="8" t="str">
         <f>IF(ISBLANK(B296),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B296))</f>
         <v/>
@@ -5350,7 +5430,7 @@
       <c r="F296" s="17"/>
       <c r="G296" s="17"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7">
       <c r="A297" s="18" t="str">
         <f>IF(ISBLANK(B297),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B297))</f>
         <v/>
@@ -5362,7 +5442,7 @@
       <c r="F297" s="20"/>
       <c r="G297" s="20"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7">
       <c r="A298" s="8" t="str">
         <f>IF(ISBLANK(B298),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B298))</f>
         <v/>
@@ -5373,7 +5453,7 @@
       <c r="F298" s="17"/>
       <c r="G298" s="17"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7">
       <c r="A299" s="18" t="str">
         <f>IF(ISBLANK(B299),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B299))</f>
         <v/>
@@ -5385,7 +5465,7 @@
       <c r="F299" s="20"/>
       <c r="G299" s="20"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7">
       <c r="A300" s="8" t="str">
         <f>IF(ISBLANK(B300),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B300))</f>
         <v/>
@@ -5396,7 +5476,7 @@
       <c r="F300" s="17"/>
       <c r="G300" s="17"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7">
       <c r="A301" s="18" t="str">
         <f>IF(ISBLANK(B301),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B301))</f>
         <v/>
@@ -5408,7 +5488,7 @@
       <c r="F301" s="20"/>
       <c r="G301" s="20"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7">
       <c r="A302" s="8" t="str">
         <f>IF(ISBLANK(B302),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B302))</f>
         <v/>
@@ -5419,7 +5499,7 @@
       <c r="F302" s="17"/>
       <c r="G302" s="17"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7">
       <c r="A303" s="18" t="str">
         <f>IF(ISBLANK(B303),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B303))</f>
         <v/>
@@ -5431,7 +5511,7 @@
       <c r="F303" s="20"/>
       <c r="G303" s="20"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7">
       <c r="A304" s="8" t="str">
         <f>IF(ISBLANK(B304),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B304))</f>
         <v/>
@@ -5442,7 +5522,7 @@
       <c r="F304" s="17"/>
       <c r="G304" s="17"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7">
       <c r="A305" s="18" t="str">
         <f>IF(ISBLANK(B305),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B305))</f>
         <v/>
@@ -5454,7 +5534,7 @@
       <c r="F305" s="20"/>
       <c r="G305" s="20"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7">
       <c r="A306" s="8" t="str">
         <f>IF(ISBLANK(B306),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B306))</f>
         <v/>
@@ -5465,7 +5545,7 @@
       <c r="F306" s="17"/>
       <c r="G306" s="17"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7">
       <c r="A307" s="18" t="str">
         <f>IF(ISBLANK(B307),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B307))</f>
         <v/>
@@ -5477,7 +5557,7 @@
       <c r="F307" s="20"/>
       <c r="G307" s="20"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7">
       <c r="A308" s="8" t="str">
         <f>IF(ISBLANK(B308),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B308))</f>
         <v/>
@@ -5488,7 +5568,7 @@
       <c r="F308" s="17"/>
       <c r="G308" s="17"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7">
       <c r="A309" s="18" t="str">
         <f>IF(ISBLANK(B309),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B309))</f>
         <v/>
@@ -5500,7 +5580,7 @@
       <c r="F309" s="20"/>
       <c r="G309" s="20"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7">
       <c r="A310" s="8" t="str">
         <f>IF(ISBLANK(B310),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B310))</f>
         <v/>
@@ -5511,7 +5591,7 @@
       <c r="F310" s="17"/>
       <c r="G310" s="17"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7">
       <c r="A311" s="18" t="str">
         <f>IF(ISBLANK(B311),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B311))</f>
         <v/>
@@ -5523,7 +5603,7 @@
       <c r="F311" s="20"/>
       <c r="G311" s="20"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7">
       <c r="A312" s="8" t="str">
         <f>IF(ISBLANK(B312),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B312))</f>
         <v/>
@@ -5534,7 +5614,7 @@
       <c r="F312" s="17"/>
       <c r="G312" s="17"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7">
       <c r="A313" s="18" t="str">
         <f>IF(ISBLANK(B313),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B313))</f>
         <v/>
@@ -5546,7 +5626,7 @@
       <c r="F313" s="20"/>
       <c r="G313" s="20"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7">
       <c r="A314" s="8" t="str">
         <f>IF(ISBLANK(B314),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B314))</f>
         <v/>
@@ -5557,7 +5637,7 @@
       <c r="F314" s="17"/>
       <c r="G314" s="17"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7">
       <c r="A315" s="18" t="str">
         <f>IF(ISBLANK(B315),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B315))</f>
         <v/>
@@ -5569,7 +5649,7 @@
       <c r="F315" s="20"/>
       <c r="G315" s="20"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7">
       <c r="A316" s="8" t="str">
         <f>IF(ISBLANK(B316),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B316))</f>
         <v/>
@@ -5580,7 +5660,7 @@
       <c r="F316" s="17"/>
       <c r="G316" s="17"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7">
       <c r="A317" s="18" t="str">
         <f>IF(ISBLANK(B317),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B317))</f>
         <v/>
@@ -5592,7 +5672,7 @@
       <c r="F317" s="20"/>
       <c r="G317" s="20"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7">
       <c r="A318" s="8" t="str">
         <f>IF(ISBLANK(B318),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B318))</f>
         <v/>
@@ -5603,7 +5683,7 @@
       <c r="F318" s="17"/>
       <c r="G318" s="17"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7">
       <c r="A319" s="18" t="str">
         <f>IF(ISBLANK(B319),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B319))</f>
         <v/>
@@ -5615,7 +5695,7 @@
       <c r="F319" s="20"/>
       <c r="G319" s="20"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7">
       <c r="A320" s="8" t="str">
         <f>IF(ISBLANK(B320),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B320))</f>
         <v/>
@@ -5626,7 +5706,7 @@
       <c r="F320" s="17"/>
       <c r="G320" s="17"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7">
       <c r="A321" s="18" t="str">
         <f>IF(ISBLANK(B321),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B321))</f>
         <v/>
@@ -5638,7 +5718,7 @@
       <c r="F321" s="20"/>
       <c r="G321" s="20"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7">
       <c r="A322" s="8" t="str">
         <f>IF(ISBLANK(B322),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B322))</f>
         <v/>
@@ -5649,7 +5729,7 @@
       <c r="F322" s="17"/>
       <c r="G322" s="17"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7">
       <c r="A323" s="18" t="str">
         <f>IF(ISBLANK(B323),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B323))</f>
         <v/>
@@ -5661,7 +5741,7 @@
       <c r="F323" s="20"/>
       <c r="G323" s="20"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7">
       <c r="A324" s="8" t="str">
         <f>IF(ISBLANK(B324),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B324))</f>
         <v/>
@@ -5672,7 +5752,7 @@
       <c r="F324" s="17"/>
       <c r="G324" s="17"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7">
       <c r="A325" s="18" t="str">
         <f>IF(ISBLANK(B325),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B325))</f>
         <v/>
@@ -5684,7 +5764,7 @@
       <c r="F325" s="20"/>
       <c r="G325" s="20"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7">
       <c r="A326" s="8" t="str">
         <f>IF(ISBLANK(B326),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B326))</f>
         <v/>
@@ -5695,7 +5775,7 @@
       <c r="F326" s="17"/>
       <c r="G326" s="17"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7">
       <c r="A327" s="18" t="str">
         <f>IF(ISBLANK(B327),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B327))</f>
         <v/>
@@ -5707,7 +5787,7 @@
       <c r="F327" s="20"/>
       <c r="G327" s="20"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7">
       <c r="A328" s="8" t="str">
         <f>IF(ISBLANK(B328),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B328))</f>
         <v/>
@@ -5718,7 +5798,7 @@
       <c r="F328" s="17"/>
       <c r="G328" s="17"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7">
       <c r="A329" s="18" t="str">
         <f>IF(ISBLANK(B329),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B329))</f>
         <v/>
@@ -5730,7 +5810,7 @@
       <c r="F329" s="20"/>
       <c r="G329" s="20"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7">
       <c r="A330" s="8" t="str">
         <f>IF(ISBLANK(B330),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B330))</f>
         <v/>
@@ -5741,7 +5821,7 @@
       <c r="F330" s="17"/>
       <c r="G330" s="17"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7">
       <c r="A331" s="18" t="str">
         <f>IF(ISBLANK(B331),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B331))</f>
         <v/>
@@ -5753,7 +5833,7 @@
       <c r="F331" s="20"/>
       <c r="G331" s="20"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7">
       <c r="A332" s="8" t="str">
         <f>IF(ISBLANK(B332),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B332))</f>
         <v/>
@@ -5764,7 +5844,7 @@
       <c r="F332" s="17"/>
       <c r="G332" s="17"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7">
       <c r="A333" s="18" t="str">
         <f>IF(ISBLANK(B333),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B333))</f>
         <v/>
@@ -5776,7 +5856,7 @@
       <c r="F333" s="20"/>
       <c r="G333" s="20"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7">
       <c r="A334" s="8" t="str">
         <f>IF(ISBLANK(B334),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B334))</f>
         <v/>
@@ -5787,7 +5867,7 @@
       <c r="F334" s="17"/>
       <c r="G334" s="17"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7">
       <c r="A335" s="18" t="str">
         <f>IF(ISBLANK(B335),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B335))</f>
         <v/>
@@ -5799,7 +5879,7 @@
       <c r="F335" s="20"/>
       <c r="G335" s="20"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7">
       <c r="A336" s="8" t="str">
         <f>IF(ISBLANK(B336),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B336))</f>
         <v/>
@@ -5810,7 +5890,7 @@
       <c r="F336" s="17"/>
       <c r="G336" s="17"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7">
       <c r="A337" s="18" t="str">
         <f>IF(ISBLANK(B337),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B337))</f>
         <v/>
@@ -5822,7 +5902,7 @@
       <c r="F337" s="20"/>
       <c r="G337" s="20"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7">
       <c r="A338" s="8" t="str">
         <f>IF(ISBLANK(B338),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B338))</f>
         <v/>
@@ -5833,7 +5913,7 @@
       <c r="F338" s="17"/>
       <c r="G338" s="17"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7">
       <c r="A339" s="18" t="str">
         <f>IF(ISBLANK(B339),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B339))</f>
         <v/>
@@ -5845,7 +5925,7 @@
       <c r="F339" s="20"/>
       <c r="G339" s="20"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7">
       <c r="A340" s="8" t="str">
         <f>IF(ISBLANK(B340),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B340))</f>
         <v/>
@@ -5856,7 +5936,7 @@
       <c r="F340" s="17"/>
       <c r="G340" s="17"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7">
       <c r="A341" s="18" t="str">
         <f>IF(ISBLANK(B341),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B341))</f>
         <v/>
@@ -5868,7 +5948,7 @@
       <c r="F341" s="20"/>
       <c r="G341" s="20"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7">
       <c r="A342" s="8" t="str">
         <f>IF(ISBLANK(B342),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B342))</f>
         <v/>
@@ -5879,7 +5959,7 @@
       <c r="F342" s="17"/>
       <c r="G342" s="17"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7">
       <c r="A343" s="18" t="str">
         <f>IF(ISBLANK(B343),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B343))</f>
         <v/>
@@ -5891,7 +5971,7 @@
       <c r="F343" s="20"/>
       <c r="G343" s="20"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7">
       <c r="A344" s="8" t="str">
         <f>IF(ISBLANK(B344),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B344))</f>
         <v/>
@@ -5902,7 +5982,7 @@
       <c r="F344" s="17"/>
       <c r="G344" s="17"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7">
       <c r="A345" s="18" t="str">
         <f>IF(ISBLANK(B345),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B345))</f>
         <v/>
@@ -5914,7 +5994,7 @@
       <c r="F345" s="20"/>
       <c r="G345" s="20"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7">
       <c r="A346" s="8" t="str">
         <f>IF(ISBLANK(B346),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B346))</f>
         <v/>
@@ -5925,7 +6005,7 @@
       <c r="F346" s="17"/>
       <c r="G346" s="17"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7">
       <c r="A347" s="18" t="str">
         <f>IF(ISBLANK(B347),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B347))</f>
         <v/>
@@ -5937,7 +6017,7 @@
       <c r="F347" s="20"/>
       <c r="G347" s="20"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7">
       <c r="A348" s="8" t="str">
         <f>IF(ISBLANK(B348),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B348))</f>
         <v/>
@@ -5948,7 +6028,7 @@
       <c r="F348" s="17"/>
       <c r="G348" s="17"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7">
       <c r="A349" s="18" t="str">
         <f>IF(ISBLANK(B349),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B349))</f>
         <v/>
@@ -5960,7 +6040,7 @@
       <c r="F349" s="20"/>
       <c r="G349" s="20"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7">
       <c r="A350" s="8" t="str">
         <f>IF(ISBLANK(B350),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B350))</f>
         <v/>
@@ -5971,7 +6051,7 @@
       <c r="F350" s="17"/>
       <c r="G350" s="17"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7">
       <c r="A351" s="18" t="str">
         <f>IF(ISBLANK(B351),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B351))</f>
         <v/>
@@ -5983,7 +6063,7 @@
       <c r="F351" s="20"/>
       <c r="G351" s="20"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7">
       <c r="A352" s="8" t="str">
         <f>IF(ISBLANK(B352),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B352))</f>
         <v/>
@@ -5994,7 +6074,7 @@
       <c r="F352" s="17"/>
       <c r="G352" s="17"/>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7">
       <c r="A353" s="18" t="str">
         <f>IF(ISBLANK(B353),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B353))</f>
         <v/>
@@ -6006,7 +6086,7 @@
       <c r="F353" s="20"/>
       <c r="G353" s="20"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7">
       <c r="A354" s="8" t="str">
         <f>IF(ISBLANK(B354),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B354))</f>
         <v/>
@@ -6017,7 +6097,7 @@
       <c r="F354" s="17"/>
       <c r="G354" s="17"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7">
       <c r="A355" s="18" t="str">
         <f>IF(ISBLANK(B355),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B355))</f>
         <v/>
@@ -6029,7 +6109,7 @@
       <c r="F355" s="20"/>
       <c r="G355" s="20"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7">
       <c r="A356" s="8" t="str">
         <f>IF(ISBLANK(B356),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B356))</f>
         <v/>
@@ -6040,7 +6120,7 @@
       <c r="F356" s="17"/>
       <c r="G356" s="17"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7">
       <c r="A357" s="18" t="str">
         <f>IF(ISBLANK(B357),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B357))</f>
         <v/>
@@ -6052,7 +6132,7 @@
       <c r="F357" s="20"/>
       <c r="G357" s="20"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7">
       <c r="A358" s="8" t="str">
         <f>IF(ISBLANK(B358),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B358))</f>
         <v/>
@@ -6063,7 +6143,7 @@
       <c r="F358" s="17"/>
       <c r="G358" s="17"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7">
       <c r="A359" s="18" t="str">
         <f>IF(ISBLANK(B359),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B359))</f>
         <v/>
@@ -6075,7 +6155,7 @@
       <c r="F359" s="20"/>
       <c r="G359" s="20"/>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7">
       <c r="A360" s="8" t="str">
         <f>IF(ISBLANK(B360),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B360))</f>
         <v/>
@@ -6086,7 +6166,7 @@
       <c r="F360" s="17"/>
       <c r="G360" s="17"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7">
       <c r="A361" s="18" t="str">
         <f>IF(ISBLANK(B361),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B361))</f>
         <v/>
@@ -6098,7 +6178,7 @@
       <c r="F361" s="20"/>
       <c r="G361" s="20"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7">
       <c r="A362" s="8" t="str">
         <f>IF(ISBLANK(B362),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B362))</f>
         <v/>
@@ -6109,7 +6189,7 @@
       <c r="F362" s="17"/>
       <c r="G362" s="17"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7">
       <c r="A363" s="18" t="str">
         <f>IF(ISBLANK(B363),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B363))</f>
         <v/>
@@ -6121,7 +6201,7 @@
       <c r="F363" s="20"/>
       <c r="G363" s="20"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7">
       <c r="A364" s="8" t="str">
         <f>IF(ISBLANK(B364),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B364))</f>
         <v/>
@@ -6132,7 +6212,7 @@
       <c r="F364" s="17"/>
       <c r="G364" s="17"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7">
       <c r="A365" s="18" t="str">
         <f>IF(ISBLANK(B365),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B365))</f>
         <v/>
@@ -6144,7 +6224,7 @@
       <c r="F365" s="20"/>
       <c r="G365" s="20"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7">
       <c r="A366" s="8" t="str">
         <f>IF(ISBLANK(B366),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B366))</f>
         <v/>
@@ -6155,7 +6235,7 @@
       <c r="F366" s="17"/>
       <c r="G366" s="17"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7">
       <c r="A367" s="18" t="str">
         <f>IF(ISBLANK(B367),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B367))</f>
         <v/>
@@ -6167,7 +6247,7 @@
       <c r="F367" s="20"/>
       <c r="G367" s="20"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7">
       <c r="A368" s="8" t="str">
         <f>IF(ISBLANK(B368),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B368))</f>
         <v/>
@@ -6178,7 +6258,7 @@
       <c r="F368" s="17"/>
       <c r="G368" s="17"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7">
       <c r="A369" s="18" t="str">
         <f>IF(ISBLANK(B369),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B369))</f>
         <v/>
@@ -6190,7 +6270,7 @@
       <c r="F369" s="20"/>
       <c r="G369" s="20"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7">
       <c r="A370" s="8" t="str">
         <f>IF(ISBLANK(B370),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B370))</f>
         <v/>
@@ -6201,7 +6281,7 @@
       <c r="F370" s="17"/>
       <c r="G370" s="17"/>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7">
       <c r="A371" s="18" t="str">
         <f>IF(ISBLANK(B371),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B371))</f>
         <v/>
@@ -6213,7 +6293,7 @@
       <c r="F371" s="20"/>
       <c r="G371" s="20"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7">
       <c r="A372" s="8" t="str">
         <f>IF(ISBLANK(B372),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B372))</f>
         <v/>
@@ -6224,7 +6304,7 @@
       <c r="F372" s="17"/>
       <c r="G372" s="17"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7">
       <c r="A373" s="18" t="str">
         <f>IF(ISBLANK(B373),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B373))</f>
         <v/>
@@ -6236,7 +6316,7 @@
       <c r="F373" s="20"/>
       <c r="G373" s="20"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7">
       <c r="A374" s="8" t="str">
         <f>IF(ISBLANK(B374),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B374))</f>
         <v/>
@@ -6247,7 +6327,7 @@
       <c r="F374" s="17"/>
       <c r="G374" s="17"/>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7">
       <c r="A375" s="18" t="str">
         <f>IF(ISBLANK(B375),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B375))</f>
         <v/>
@@ -6259,7 +6339,7 @@
       <c r="F375" s="20"/>
       <c r="G375" s="20"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7">
       <c r="A376" s="8" t="str">
         <f>IF(ISBLANK(B376),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B376))</f>
         <v/>
@@ -6270,7 +6350,7 @@
       <c r="F376" s="17"/>
       <c r="G376" s="17"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7">
       <c r="A377" s="18" t="str">
         <f>IF(ISBLANK(B377),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B377))</f>
         <v/>
@@ -6282,7 +6362,7 @@
       <c r="F377" s="20"/>
       <c r="G377" s="20"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7">
       <c r="A378" s="8" t="str">
         <f>IF(ISBLANK(B378),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B378))</f>
         <v/>
@@ -6293,7 +6373,7 @@
       <c r="F378" s="17"/>
       <c r="G378" s="17"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7">
       <c r="A379" s="18" t="str">
         <f>IF(ISBLANK(B379),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B379))</f>
         <v/>
@@ -6305,7 +6385,7 @@
       <c r="F379" s="20"/>
       <c r="G379" s="20"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7">
       <c r="A380" s="8" t="str">
         <f>IF(ISBLANK(B380),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B380))</f>
         <v/>
@@ -6316,7 +6396,7 @@
       <c r="F380" s="17"/>
       <c r="G380" s="17"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7">
       <c r="A381" s="18" t="str">
         <f>IF(ISBLANK(B381),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B381))</f>
         <v/>
@@ -6328,7 +6408,7 @@
       <c r="F381" s="20"/>
       <c r="G381" s="20"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7">
       <c r="A382" s="8" t="str">
         <f>IF(ISBLANK(B382),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B382))</f>
         <v/>
@@ -6339,7 +6419,7 @@
       <c r="F382" s="17"/>
       <c r="G382" s="17"/>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7">
       <c r="A383" s="18" t="str">
         <f>IF(ISBLANK(B383),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B383))</f>
         <v/>
@@ -6351,7 +6431,7 @@
       <c r="F383" s="20"/>
       <c r="G383" s="20"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7">
       <c r="A384" s="8" t="str">
         <f>IF(ISBLANK(B384),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B384))</f>
         <v/>
@@ -6362,7 +6442,7 @@
       <c r="F384" s="17"/>
       <c r="G384" s="17"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7">
       <c r="A385" s="18" t="str">
         <f>IF(ISBLANK(B385),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B385))</f>
         <v/>
@@ -6374,7 +6454,7 @@
       <c r="F385" s="20"/>
       <c r="G385" s="20"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7">
       <c r="A386" s="8" t="str">
         <f>IF(ISBLANK(B386),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B386))</f>
         <v/>
@@ -6385,7 +6465,7 @@
       <c r="F386" s="17"/>
       <c r="G386" s="17"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7">
       <c r="A387" s="18" t="str">
         <f>IF(ISBLANK(B387),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B387))</f>
         <v/>
@@ -6397,7 +6477,7 @@
       <c r="F387" s="20"/>
       <c r="G387" s="20"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7">
       <c r="A388" s="8" t="str">
         <f>IF(ISBLANK(B388),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B388))</f>
         <v/>
@@ -6408,7 +6488,7 @@
       <c r="F388" s="17"/>
       <c r="G388" s="17"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7">
       <c r="A389" s="18" t="str">
         <f>IF(ISBLANK(B389),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B389))</f>
         <v/>
@@ -6420,7 +6500,7 @@
       <c r="F389" s="20"/>
       <c r="G389" s="20"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7">
       <c r="A390" s="8" t="str">
         <f>IF(ISBLANK(B390),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B390))</f>
         <v/>
@@ -6431,7 +6511,7 @@
       <c r="F390" s="17"/>
       <c r="G390" s="17"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7">
       <c r="A391" s="18" t="str">
         <f>IF(ISBLANK(B391),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B391))</f>
         <v/>
@@ -6443,7 +6523,7 @@
       <c r="F391" s="20"/>
       <c r="G391" s="20"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7">
       <c r="A392" s="8" t="str">
         <f>IF(ISBLANK(B392),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B392))</f>
         <v/>
@@ -6454,7 +6534,7 @@
       <c r="F392" s="17"/>
       <c r="G392" s="17"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7">
       <c r="A393" s="18" t="str">
         <f>IF(ISBLANK(B393),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B393))</f>
         <v/>
@@ -6466,7 +6546,7 @@
       <c r="F393" s="20"/>
       <c r="G393" s="20"/>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7">
       <c r="A394" s="8" t="str">
         <f>IF(ISBLANK(B394),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B394))</f>
         <v/>
@@ -6477,7 +6557,7 @@
       <c r="F394" s="17"/>
       <c r="G394" s="17"/>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7">
       <c r="A395" s="18" t="str">
         <f>IF(ISBLANK(B395),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B395))</f>
         <v/>
@@ -6489,7 +6569,7 @@
       <c r="F395" s="20"/>
       <c r="G395" s="20"/>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7">
       <c r="A396" s="8" t="str">
         <f>IF(ISBLANK(B396),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B396))</f>
         <v/>
@@ -6500,7 +6580,7 @@
       <c r="F396" s="17"/>
       <c r="G396" s="17"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7">
       <c r="A397" s="18" t="str">
         <f>IF(ISBLANK(B397),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B397))</f>
         <v/>
@@ -6512,7 +6592,7 @@
       <c r="F397" s="20"/>
       <c r="G397" s="20"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7">
       <c r="A398" s="8" t="str">
         <f>IF(ISBLANK(B398),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B398))</f>
         <v/>
@@ -6523,7 +6603,7 @@
       <c r="F398" s="17"/>
       <c r="G398" s="17"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7">
       <c r="A399" s="18" t="str">
         <f>IF(ISBLANK(B399),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B399))</f>
         <v/>
@@ -6535,7 +6615,7 @@
       <c r="F399" s="20"/>
       <c r="G399" s="20"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7">
       <c r="A400" s="8" t="str">
         <f>IF(ISBLANK(B400),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B400))</f>
         <v/>
@@ -6546,7 +6626,7 @@
       <c r="F400" s="17"/>
       <c r="G400" s="17"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7">
       <c r="A401" s="18" t="str">
         <f>IF(ISBLANK(B401),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B401))</f>
         <v/>
@@ -6558,7 +6638,7 @@
       <c r="F401" s="20"/>
       <c r="G401" s="20"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7">
       <c r="A402" s="8" t="str">
         <f>IF(ISBLANK(B402),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B402))</f>
         <v/>
@@ -6569,7 +6649,7 @@
       <c r="F402" s="17"/>
       <c r="G402" s="17"/>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7">
       <c r="A403" s="18" t="str">
         <f>IF(ISBLANK(B403),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B403))</f>
         <v/>
@@ -6581,7 +6661,7 @@
       <c r="F403" s="20"/>
       <c r="G403" s="20"/>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7">
       <c r="A404" s="8" t="str">
         <f>IF(ISBLANK(B404),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B404))</f>
         <v/>
@@ -6592,7 +6672,7 @@
       <c r="F404" s="17"/>
       <c r="G404" s="17"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7">
       <c r="A405" s="18" t="str">
         <f>IF(ISBLANK(B405),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B405))</f>
         <v/>
@@ -6604,7 +6684,7 @@
       <c r="F405" s="20"/>
       <c r="G405" s="20"/>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7">
       <c r="A406" s="8" t="str">
         <f>IF(ISBLANK(B406),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B406))</f>
         <v/>
@@ -6615,7 +6695,7 @@
       <c r="F406" s="17"/>
       <c r="G406" s="17"/>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7">
       <c r="A407" s="18" t="str">
         <f>IF(ISBLANK(B407),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B407))</f>
         <v/>
@@ -6627,7 +6707,7 @@
       <c r="F407" s="20"/>
       <c r="G407" s="20"/>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7">
       <c r="A408" s="8" t="str">
         <f>IF(ISBLANK(B408),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B408))</f>
         <v/>
@@ -6638,7 +6718,7 @@
       <c r="F408" s="17"/>
       <c r="G408" s="17"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7">
       <c r="A409" s="18" t="str">
         <f>IF(ISBLANK(B409),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B409))</f>
         <v/>
@@ -6650,7 +6730,7 @@
       <c r="F409" s="20"/>
       <c r="G409" s="20"/>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7">
       <c r="A410" s="8" t="str">
         <f>IF(ISBLANK(B410),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B410))</f>
         <v/>
@@ -6661,7 +6741,7 @@
       <c r="F410" s="17"/>
       <c r="G410" s="17"/>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7">
       <c r="A411" s="18" t="str">
         <f>IF(ISBLANK(B411),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B411))</f>
         <v/>
@@ -6673,7 +6753,7 @@
       <c r="F411" s="20"/>
       <c r="G411" s="20"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7">
       <c r="A412" s="8" t="str">
         <f>IF(ISBLANK(B412),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B412))</f>
         <v/>
@@ -6684,7 +6764,7 @@
       <c r="F412" s="17"/>
       <c r="G412" s="17"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7">
       <c r="A413" s="18" t="str">
         <f>IF(ISBLANK(B413),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B413))</f>
         <v/>
@@ -6696,7 +6776,7 @@
       <c r="F413" s="20"/>
       <c r="G413" s="20"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7">
       <c r="A414" s="8" t="str">
         <f>IF(ISBLANK(B414),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B414))</f>
         <v/>
@@ -6707,7 +6787,7 @@
       <c r="F414" s="17"/>
       <c r="G414" s="17"/>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7">
       <c r="A415" s="18" t="str">
         <f>IF(ISBLANK(B415),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B415))</f>
         <v/>
@@ -6719,7 +6799,7 @@
       <c r="F415" s="20"/>
       <c r="G415" s="20"/>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7">
       <c r="A416" s="8" t="str">
         <f>IF(ISBLANK(B416),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B416))</f>
         <v/>
@@ -6730,7 +6810,7 @@
       <c r="F416" s="17"/>
       <c r="G416" s="17"/>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7">
       <c r="A417" s="18" t="str">
         <f>IF(ISBLANK(B417),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B417))</f>
         <v/>
@@ -6742,7 +6822,7 @@
       <c r="F417" s="20"/>
       <c r="G417" s="20"/>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7">
       <c r="A418" s="8" t="str">
         <f>IF(ISBLANK(B418),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B418))</f>
         <v/>
@@ -6753,7 +6833,7 @@
       <c r="F418" s="17"/>
       <c r="G418" s="17"/>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7">
       <c r="A419" s="18" t="str">
         <f>IF(ISBLANK(B419),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B419))</f>
         <v/>
@@ -6765,7 +6845,7 @@
       <c r="F419" s="20"/>
       <c r="G419" s="20"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7">
       <c r="A420" s="8" t="str">
         <f>IF(ISBLANK(B420),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B420))</f>
         <v/>
@@ -6776,7 +6856,7 @@
       <c r="F420" s="17"/>
       <c r="G420" s="17"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7">
       <c r="A421" s="18" t="str">
         <f>IF(ISBLANK(B421),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B421))</f>
         <v/>
@@ -6788,7 +6868,7 @@
       <c r="F421" s="20"/>
       <c r="G421" s="20"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7">
       <c r="A422" s="8" t="str">
         <f>IF(ISBLANK(B422),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B422))</f>
         <v/>
@@ -6799,7 +6879,7 @@
       <c r="F422" s="17"/>
       <c r="G422" s="17"/>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7">
       <c r="A423" s="18" t="str">
         <f>IF(ISBLANK(B423),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B423))</f>
         <v/>
@@ -6811,7 +6891,7 @@
       <c r="F423" s="20"/>
       <c r="G423" s="20"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7">
       <c r="A424" s="8" t="str">
         <f>IF(ISBLANK(B424),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B424))</f>
         <v/>
@@ -6822,7 +6902,7 @@
       <c r="F424" s="17"/>
       <c r="G424" s="17"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7">
       <c r="A425" s="18" t="str">
         <f>IF(ISBLANK(B425),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B425))</f>
         <v/>
@@ -6834,7 +6914,7 @@
       <c r="F425" s="20"/>
       <c r="G425" s="20"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7">
       <c r="A426" s="8" t="str">
         <f>IF(ISBLANK(B426),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B426))</f>
         <v/>
@@ -6845,7 +6925,7 @@
       <c r="F426" s="17"/>
       <c r="G426" s="17"/>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7">
       <c r="A427" s="18" t="str">
         <f>IF(ISBLANK(B427),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B427))</f>
         <v/>
@@ -6857,7 +6937,7 @@
       <c r="F427" s="20"/>
       <c r="G427" s="20"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7">
       <c r="A428" s="8" t="str">
         <f>IF(ISBLANK(B428),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B428))</f>
         <v/>
@@ -6868,7 +6948,7 @@
       <c r="F428" s="17"/>
       <c r="G428" s="17"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7">
       <c r="A429" s="18" t="str">
         <f>IF(ISBLANK(B429),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B429))</f>
         <v/>
@@ -6880,7 +6960,7 @@
       <c r="F429" s="20"/>
       <c r="G429" s="20"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7">
       <c r="A430" s="8" t="str">
         <f>IF(ISBLANK(B430),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B430))</f>
         <v/>
@@ -6891,7 +6971,7 @@
       <c r="F430" s="17"/>
       <c r="G430" s="17"/>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7">
       <c r="A431" s="18" t="str">
         <f>IF(ISBLANK(B431),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B431))</f>
         <v/>
@@ -6903,7 +6983,7 @@
       <c r="F431" s="20"/>
       <c r="G431" s="20"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7">
       <c r="A432" s="8" t="str">
         <f>IF(ISBLANK(B432),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B432))</f>
         <v/>
@@ -6914,7 +6994,7 @@
       <c r="F432" s="17"/>
       <c r="G432" s="17"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7">
       <c r="A433" s="18" t="str">
         <f>IF(ISBLANK(B433),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B433))</f>
         <v/>
@@ -6926,7 +7006,7 @@
       <c r="F433" s="20"/>
       <c r="G433" s="20"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7">
       <c r="A434" s="8" t="str">
         <f>IF(ISBLANK(B434),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B434))</f>
         <v/>
@@ -6937,7 +7017,7 @@
       <c r="F434" s="17"/>
       <c r="G434" s="17"/>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7">
       <c r="A435" s="18" t="str">
         <f>IF(ISBLANK(B435),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B435))</f>
         <v/>
@@ -6949,7 +7029,7 @@
       <c r="F435" s="20"/>
       <c r="G435" s="20"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7">
       <c r="A436" s="8" t="str">
         <f>IF(ISBLANK(B436),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B436))</f>
         <v/>
@@ -6960,7 +7040,7 @@
       <c r="F436" s="17"/>
       <c r="G436" s="17"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7">
       <c r="A437" s="18" t="str">
         <f>IF(ISBLANK(B437),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B437))</f>
         <v/>
@@ -6972,7 +7052,7 @@
       <c r="F437" s="20"/>
       <c r="G437" s="20"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7">
       <c r="A438" s="8" t="str">
         <f>IF(ISBLANK(B438),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B438))</f>
         <v/>
@@ -6983,7 +7063,7 @@
       <c r="F438" s="17"/>
       <c r="G438" s="17"/>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7">
       <c r="A439" s="18" t="str">
         <f>IF(ISBLANK(B439),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B439))</f>
         <v/>
@@ -6995,7 +7075,7 @@
       <c r="F439" s="20"/>
       <c r="G439" s="20"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7">
       <c r="A440" s="8" t="str">
         <f>IF(ISBLANK(B440),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B440))</f>
         <v/>
@@ -7006,7 +7086,7 @@
       <c r="F440" s="17"/>
       <c r="G440" s="17"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7">
       <c r="A441" s="18" t="str">
         <f>IF(ISBLANK(B441),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B441))</f>
         <v/>
@@ -7018,7 +7098,7 @@
       <c r="F441" s="20"/>
       <c r="G441" s="20"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7">
       <c r="A442" s="8" t="str">
         <f>IF(ISBLANK(B442),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B442))</f>
         <v/>
@@ -7029,7 +7109,7 @@
       <c r="F442" s="17"/>
       <c r="G442" s="17"/>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7">
       <c r="A443" s="18" t="str">
         <f>IF(ISBLANK(B443),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B443))</f>
         <v/>
@@ -7041,7 +7121,7 @@
       <c r="F443" s="20"/>
       <c r="G443" s="20"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7">
       <c r="A444" s="8" t="str">
         <f>IF(ISBLANK(B444),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B444))</f>
         <v/>
@@ -7052,7 +7132,7 @@
       <c r="F444" s="17"/>
       <c r="G444" s="17"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7">
       <c r="A445" s="18" t="str">
         <f>IF(ISBLANK(B445),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B445))</f>
         <v/>
@@ -7064,7 +7144,7 @@
       <c r="F445" s="20"/>
       <c r="G445" s="20"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7">
       <c r="A446" s="8" t="str">
         <f>IF(ISBLANK(B446),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B446))</f>
         <v/>
@@ -7075,7 +7155,7 @@
       <c r="F446" s="17"/>
       <c r="G446" s="17"/>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7">
       <c r="A447" s="18" t="str">
         <f>IF(ISBLANK(B447),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B447))</f>
         <v/>
@@ -7087,7 +7167,7 @@
       <c r="F447" s="20"/>
       <c r="G447" s="20"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7">
       <c r="A448" s="8" t="str">
         <f>IF(ISBLANK(B448),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B448))</f>
         <v/>
@@ -7098,7 +7178,7 @@
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7">
       <c r="A449" s="18" t="str">
         <f>IF(ISBLANK(B449),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B449))</f>
         <v/>
@@ -7110,7 +7190,7 @@
       <c r="F449" s="20"/>
       <c r="G449" s="20"/>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7">
       <c r="A450" s="8" t="str">
         <f>IF(ISBLANK(B450),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B450))</f>
         <v/>
@@ -7121,7 +7201,7 @@
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7">
       <c r="A451" s="18" t="str">
         <f>IF(ISBLANK(B451),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B451))</f>
         <v/>
@@ -7133,7 +7213,7 @@
       <c r="F451" s="20"/>
       <c r="G451" s="20"/>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7">
       <c r="A452" s="8" t="str">
         <f>IF(ISBLANK(B452),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B452))</f>
         <v/>
@@ -7144,7 +7224,7 @@
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7">
       <c r="A453" s="18" t="str">
         <f>IF(ISBLANK(B453),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B453))</f>
         <v/>
@@ -7156,7 +7236,7 @@
       <c r="F453" s="20"/>
       <c r="G453" s="20"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7">
       <c r="A454" s="8" t="str">
         <f>IF(ISBLANK(B454),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B454))</f>
         <v/>
@@ -7167,7 +7247,7 @@
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7">
       <c r="A455" s="18" t="str">
         <f>IF(ISBLANK(B455),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B455))</f>
         <v/>
@@ -7179,7 +7259,7 @@
       <c r="F455" s="20"/>
       <c r="G455" s="20"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7">
       <c r="A456" s="8" t="str">
         <f>IF(ISBLANK(B456),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B456))</f>
         <v/>
@@ -7190,7 +7270,7 @@
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7">
       <c r="A457" s="18" t="str">
         <f>IF(ISBLANK(B457),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B457))</f>
         <v/>
@@ -7202,7 +7282,7 @@
       <c r="F457" s="20"/>
       <c r="G457" s="20"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7">
       <c r="A458" s="8" t="str">
         <f>IF(ISBLANK(B458),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B458))</f>
         <v/>
@@ -7213,7 +7293,7 @@
       <c r="F458" s="17"/>
       <c r="G458" s="17"/>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7">
       <c r="A459" s="18" t="str">
         <f>IF(ISBLANK(B459),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B459))</f>
         <v/>
@@ -7225,7 +7305,7 @@
       <c r="F459" s="20"/>
       <c r="G459" s="20"/>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7">
       <c r="A460" s="8" t="str">
         <f>IF(ISBLANK(B460),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B460))</f>
         <v/>
@@ -7236,7 +7316,7 @@
       <c r="F460" s="17"/>
       <c r="G460" s="17"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7">
       <c r="A461" s="18" t="str">
         <f>IF(ISBLANK(B461),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B461))</f>
         <v/>
@@ -7248,7 +7328,7 @@
       <c r="F461" s="20"/>
       <c r="G461" s="20"/>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7">
       <c r="A462" s="8" t="str">
         <f>IF(ISBLANK(B462),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B462))</f>
         <v/>
@@ -7259,7 +7339,7 @@
       <c r="F462" s="17"/>
       <c r="G462" s="17"/>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7">
       <c r="A463" s="18" t="str">
         <f>IF(ISBLANK(B463),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B463))</f>
         <v/>
@@ -7271,7 +7351,7 @@
       <c r="F463" s="20"/>
       <c r="G463" s="20"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7">
       <c r="A464" s="8" t="str">
         <f>IF(ISBLANK(B464),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B464))</f>
         <v/>
@@ -7282,7 +7362,7 @@
       <c r="F464" s="17"/>
       <c r="G464" s="17"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7">
       <c r="A465" s="18" t="str">
         <f>IF(ISBLANK(B465),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B465))</f>
         <v/>
@@ -7294,7 +7374,7 @@
       <c r="F465" s="20"/>
       <c r="G465" s="20"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7">
       <c r="A466" s="8" t="str">
         <f>IF(ISBLANK(B466),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B466))</f>
         <v/>
@@ -7305,7 +7385,7 @@
       <c r="F466" s="17"/>
       <c r="G466" s="17"/>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7">
       <c r="A467" s="18" t="str">
         <f>IF(ISBLANK(B467),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B467))</f>
         <v/>
@@ -7317,7 +7397,7 @@
       <c r="F467" s="20"/>
       <c r="G467" s="20"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7">
       <c r="A468" s="8" t="str">
         <f>IF(ISBLANK(B468),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B468))</f>
         <v/>
@@ -7328,7 +7408,7 @@
       <c r="F468" s="17"/>
       <c r="G468" s="17"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7">
       <c r="A469" s="18" t="str">
         <f>IF(ISBLANK(B469),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B469))</f>
         <v/>
@@ -7340,7 +7420,7 @@
       <c r="F469" s="20"/>
       <c r="G469" s="20"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7">
       <c r="A470" s="8" t="str">
         <f>IF(ISBLANK(B470),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B470))</f>
         <v/>
@@ -7351,7 +7431,7 @@
       <c r="F470" s="17"/>
       <c r="G470" s="17"/>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7">
       <c r="A471" s="18" t="str">
         <f>IF(ISBLANK(B471),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B471))</f>
         <v/>
@@ -7363,7 +7443,7 @@
       <c r="F471" s="20"/>
       <c r="G471" s="20"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7">
       <c r="A472" s="8" t="str">
         <f>IF(ISBLANK(B472),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B472))</f>
         <v/>
@@ -7374,7 +7454,7 @@
       <c r="F472" s="17"/>
       <c r="G472" s="17"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7">
       <c r="A473" s="18" t="str">
         <f>IF(ISBLANK(B473),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B473))</f>
         <v/>
@@ -7386,7 +7466,7 @@
       <c r="F473" s="20"/>
       <c r="G473" s="20"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7">
       <c r="A474" s="8" t="str">
         <f>IF(ISBLANK(B474),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B474))</f>
         <v/>
@@ -7397,7 +7477,7 @@
       <c r="F474" s="17"/>
       <c r="G474" s="17"/>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7">
       <c r="A475" s="18" t="str">
         <f>IF(ISBLANK(B475),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B475))</f>
         <v/>
@@ -7409,7 +7489,7 @@
       <c r="F475" s="20"/>
       <c r="G475" s="20"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7">
       <c r="A476" s="8" t="str">
         <f>IF(ISBLANK(B476),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B476))</f>
         <v/>
@@ -7420,7 +7500,7 @@
       <c r="F476" s="17"/>
       <c r="G476" s="17"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7">
       <c r="A477" s="18" t="str">
         <f>IF(ISBLANK(B477),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B477))</f>
         <v/>
@@ -7432,7 +7512,7 @@
       <c r="F477" s="20"/>
       <c r="G477" s="20"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7">
       <c r="A478" s="8" t="str">
         <f>IF(ISBLANK(B478),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B478))</f>
         <v/>
@@ -7443,7 +7523,7 @@
       <c r="F478" s="17"/>
       <c r="G478" s="17"/>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7">
       <c r="A479" s="18" t="str">
         <f>IF(ISBLANK(B479),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B479))</f>
         <v/>
@@ -7455,7 +7535,7 @@
       <c r="F479" s="20"/>
       <c r="G479" s="20"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7">
       <c r="A480" s="8" t="str">
         <f>IF(ISBLANK(B480),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B480))</f>
         <v/>
@@ -7466,7 +7546,7 @@
       <c r="F480" s="17"/>
       <c r="G480" s="17"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7">
       <c r="A481" s="18" t="str">
         <f>IF(ISBLANK(B481),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B481))</f>
         <v/>
@@ -7478,7 +7558,7 @@
       <c r="F481" s="20"/>
       <c r="G481" s="20"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7">
       <c r="A482" s="8" t="str">
         <f>IF(ISBLANK(B482),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B482))</f>
         <v/>
@@ -7489,7 +7569,7 @@
       <c r="F482" s="17"/>
       <c r="G482" s="17"/>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7">
       <c r="A483" s="18" t="str">
         <f>IF(ISBLANK(B483),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B483))</f>
         <v/>
@@ -7501,7 +7581,7 @@
       <c r="F483" s="20"/>
       <c r="G483" s="20"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7">
       <c r="A484" s="8" t="str">
         <f>IF(ISBLANK(B484),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B484))</f>
         <v/>
@@ -7512,7 +7592,7 @@
       <c r="F484" s="17"/>
       <c r="G484" s="17"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7">
       <c r="A485" s="18" t="str">
         <f>IF(ISBLANK(B485),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B485))</f>
         <v/>
@@ -7524,7 +7604,7 @@
       <c r="F485" s="20"/>
       <c r="G485" s="20"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7">
       <c r="A486" s="8" t="str">
         <f>IF(ISBLANK(B486),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B486))</f>
         <v/>
@@ -7535,7 +7615,7 @@
       <c r="F486" s="17"/>
       <c r="G486" s="17"/>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7">
       <c r="A487" s="18" t="str">
         <f>IF(ISBLANK(B487),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B487))</f>
         <v/>
@@ -7547,7 +7627,7 @@
       <c r="F487" s="20"/>
       <c r="G487" s="20"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7">
       <c r="A488" s="8" t="str">
         <f>IF(ISBLANK(B488),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B488))</f>
         <v/>
@@ -7558,7 +7638,7 @@
       <c r="F488" s="17"/>
       <c r="G488" s="17"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7">
       <c r="A489" s="18" t="str">
         <f>IF(ISBLANK(B489),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B489))</f>
         <v/>
@@ -7570,7 +7650,7 @@
       <c r="F489" s="20"/>
       <c r="G489" s="20"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7">
       <c r="A490" s="8" t="str">
         <f>IF(ISBLANK(B490),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B490))</f>
         <v/>
@@ -7581,7 +7661,7 @@
       <c r="F490" s="17"/>
       <c r="G490" s="17"/>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7">
       <c r="A491" s="18" t="str">
         <f>IF(ISBLANK(B491),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B491))</f>
         <v/>
@@ -7593,7 +7673,7 @@
       <c r="F491" s="20"/>
       <c r="G491" s="20"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7">
       <c r="A492" s="8" t="str">
         <f>IF(ISBLANK(B492),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B492))</f>
         <v/>
@@ -7604,7 +7684,7 @@
       <c r="F492" s="17"/>
       <c r="G492" s="17"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7">
       <c r="A493" s="18" t="str">
         <f>IF(ISBLANK(B493),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B493))</f>
         <v/>
@@ -7616,7 +7696,7 @@
       <c r="F493" s="20"/>
       <c r="G493" s="20"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7">
       <c r="A494" s="8" t="str">
         <f>IF(ISBLANK(B494),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B494))</f>
         <v/>
@@ -7627,7 +7707,7 @@
       <c r="F494" s="17"/>
       <c r="G494" s="17"/>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7">
       <c r="A495" s="18" t="str">
         <f>IF(ISBLANK(B495),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B495))</f>
         <v/>
@@ -7639,7 +7719,7 @@
       <c r="F495" s="20"/>
       <c r="G495" s="20"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7">
       <c r="A496" s="8" t="str">
         <f>IF(ISBLANK(B496),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B496))</f>
         <v/>
@@ -7650,7 +7730,7 @@
       <c r="F496" s="17"/>
       <c r="G496" s="17"/>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7">
       <c r="A497" s="18" t="str">
         <f>IF(ISBLANK(B497),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B497))</f>
         <v/>
@@ -7662,7 +7742,7 @@
       <c r="F497" s="20"/>
       <c r="G497" s="20"/>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7">
       <c r="A498" s="8" t="str">
         <f>IF(ISBLANK(B498),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B498))</f>
         <v/>
@@ -7673,7 +7753,7 @@
       <c r="F498" s="17"/>
       <c r="G498" s="17"/>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7">
       <c r="A499" s="18" t="str">
         <f>IF(ISBLANK(B499),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B499))</f>
         <v/>
@@ -7685,7 +7765,7 @@
       <c r="F499" s="20"/>
       <c r="G499" s="20"/>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7">
       <c r="A500" s="8" t="str">
         <f>IF(ISBLANK(B500),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B500))</f>
         <v/>
@@ -7696,7 +7776,7 @@
       <c r="F500" s="17"/>
       <c r="G500" s="17"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7">
       <c r="A501" s="18" t="str">
         <f>IF(ISBLANK(B501),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B501))</f>
         <v/>
@@ -7708,7 +7788,7 @@
       <c r="F501" s="20"/>
       <c r="G501" s="20"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7">
       <c r="A502" s="8" t="str">
         <f>IF(ISBLANK(B502),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B502))</f>
         <v/>
@@ -7719,7 +7799,7 @@
       <c r="F502" s="17"/>
       <c r="G502" s="17"/>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7">
       <c r="A503" s="18" t="str">
         <f>IF(ISBLANK(B503),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B503))</f>
         <v/>
@@ -7731,7 +7811,7 @@
       <c r="F503" s="20"/>
       <c r="G503" s="20"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7">
       <c r="A504" s="8" t="str">
         <f>IF(ISBLANK(B504),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B504))</f>
         <v/>
@@ -7742,7 +7822,7 @@
       <c r="F504" s="17"/>
       <c r="G504" s="17"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7">
       <c r="A505" s="18" t="str">
         <f>IF(ISBLANK(B505),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B505))</f>
         <v/>
@@ -7754,7 +7834,7 @@
       <c r="F505" s="20"/>
       <c r="G505" s="20"/>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7">
       <c r="A506" s="8" t="str">
         <f>IF(ISBLANK(B506),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B506))</f>
         <v/>
@@ -7765,7 +7845,7 @@
       <c r="F506" s="17"/>
       <c r="G506" s="17"/>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7">
       <c r="A507" s="18" t="str">
         <f>IF(ISBLANK(B507),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B507))</f>
         <v/>
@@ -7777,7 +7857,7 @@
       <c r="F507" s="20"/>
       <c r="G507" s="20"/>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7">
       <c r="A508" s="8" t="str">
         <f>IF(ISBLANK(B508),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B508))</f>
         <v/>
@@ -7788,7 +7868,7 @@
       <c r="F508" s="17"/>
       <c r="G508" s="17"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7">
       <c r="A509" s="18" t="str">
         <f>IF(ISBLANK(B509),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B509))</f>
         <v/>
@@ -7800,7 +7880,7 @@
       <c r="F509" s="20"/>
       <c r="G509" s="20"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7">
       <c r="A510" s="8" t="str">
         <f>IF(ISBLANK(B510),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B510))</f>
         <v/>
@@ -7811,7 +7891,7 @@
       <c r="F510" s="17"/>
       <c r="G510" s="17"/>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7">
       <c r="A511" s="18" t="str">
         <f>IF(ISBLANK(B511),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B511))</f>
         <v/>
@@ -7823,7 +7903,7 @@
       <c r="F511" s="20"/>
       <c r="G511" s="20"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7">
       <c r="A512" s="8" t="str">
         <f>IF(ISBLANK(B512),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B512))</f>
         <v/>
@@ -7834,7 +7914,7 @@
       <c r="F512" s="17"/>
       <c r="G512" s="17"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7">
       <c r="A513" s="18" t="str">
         <f>IF(ISBLANK(B513),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B513))</f>
         <v/>
@@ -7846,7 +7926,7 @@
       <c r="F513" s="20"/>
       <c r="G513" s="20"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7">
       <c r="A514" s="8" t="str">
         <f>IF(ISBLANK(B514),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B514))</f>
         <v/>
@@ -7857,7 +7937,7 @@
       <c r="F514" s="17"/>
       <c r="G514" s="17"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7">
       <c r="A515" s="18" t="str">
         <f>IF(ISBLANK(B515),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B515))</f>
         <v/>
@@ -7869,7 +7949,7 @@
       <c r="F515" s="20"/>
       <c r="G515" s="20"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7">
       <c r="A516" s="8" t="str">
         <f>IF(ISBLANK(B516),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B516))</f>
         <v/>
@@ -7880,7 +7960,7 @@
       <c r="F516" s="17"/>
       <c r="G516" s="17"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7">
       <c r="A517" s="18" t="str">
         <f>IF(ISBLANK(B517),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B517))</f>
         <v/>
@@ -7892,7 +7972,7 @@
       <c r="F517" s="20"/>
       <c r="G517" s="20"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7">
       <c r="A518" s="8" t="str">
         <f>IF(ISBLANK(B518),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B518))</f>
         <v/>
@@ -7903,7 +7983,7 @@
       <c r="F518" s="17"/>
       <c r="G518" s="17"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7">
       <c r="A519" s="18" t="str">
         <f>IF(ISBLANK(B519),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B519))</f>
         <v/>
@@ -7915,7 +7995,7 @@
       <c r="F519" s="20"/>
       <c r="G519" s="20"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7">
       <c r="A520" s="8" t="str">
         <f>IF(ISBLANK(B520),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B520))</f>
         <v/>
@@ -7926,7 +8006,7 @@
       <c r="F520" s="17"/>
       <c r="G520" s="17"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7">
       <c r="A521" s="18" t="str">
         <f>IF(ISBLANK(B521),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B521))</f>
         <v/>
@@ -7938,7 +8018,7 @@
       <c r="F521" s="20"/>
       <c r="G521" s="20"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7">
       <c r="A522" s="8" t="str">
         <f>IF(ISBLANK(B522),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B522))</f>
         <v/>
@@ -7949,7 +8029,7 @@
       <c r="F522" s="17"/>
       <c r="G522" s="17"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7">
       <c r="A523" s="18" t="str">
         <f>IF(ISBLANK(B523),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B523))</f>
         <v/>
@@ -7961,7 +8041,7 @@
       <c r="F523" s="20"/>
       <c r="G523" s="20"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7">
       <c r="A524" s="8" t="str">
         <f>IF(ISBLANK(B524),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B524))</f>
         <v/>
@@ -7972,7 +8052,7 @@
       <c r="F524" s="17"/>
       <c r="G524" s="17"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7">
       <c r="A525" s="18" t="str">
         <f>IF(ISBLANK(B525),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B525))</f>
         <v/>
@@ -7984,7 +8064,7 @@
       <c r="F525" s="20"/>
       <c r="G525" s="20"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7">
       <c r="A526" s="8" t="str">
         <f>IF(ISBLANK(B526),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B526))</f>
         <v/>
@@ -7995,7 +8075,7 @@
       <c r="F526" s="17"/>
       <c r="G526" s="17"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7">
       <c r="A527" s="18" t="str">
         <f>IF(ISBLANK(B527),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B527))</f>
         <v/>
@@ -8007,7 +8087,7 @@
       <c r="F527" s="20"/>
       <c r="G527" s="20"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7">
       <c r="A528" s="8" t="str">
         <f>IF(ISBLANK(B528),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B528))</f>
         <v/>
@@ -8018,7 +8098,7 @@
       <c r="F528" s="17"/>
       <c r="G528" s="17"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7">
       <c r="A529" s="18" t="str">
         <f>IF(ISBLANK(B529),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B529))</f>
         <v/>
@@ -8030,7 +8110,7 @@
       <c r="F529" s="20"/>
       <c r="G529" s="20"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7">
       <c r="A530" s="8" t="str">
         <f>IF(ISBLANK(B530),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B530))</f>
         <v/>
@@ -8041,7 +8121,7 @@
       <c r="F530" s="17"/>
       <c r="G530" s="17"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7">
       <c r="A531" s="18" t="str">
         <f>IF(ISBLANK(B531),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B531))</f>
         <v/>
@@ -8053,7 +8133,7 @@
       <c r="F531" s="20"/>
       <c r="G531" s="20"/>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:7">
       <c r="A532" s="8" t="str">
         <f>IF(ISBLANK(B532),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B532))</f>
         <v/>
@@ -8119,7 +8199,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21D7432-C939-0D45-BAC2-A6A2196EA9C6}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A3:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="10.75" customWidth="1"/>
@@ -8127,7 +8207,7 @@
     <col min="4" max="4" width="13.5" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -8141,14 +8221,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C4,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B4">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C4,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C4" s="28" t="str">
         <f>'Journal de travail'!M8</f>
@@ -8156,17 +8236,17 @@
       </c>
       <c r="D4" s="45">
         <f>(A4+B4)/1440</f>
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.10416666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C5" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8174,10 +8254,10 @@
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C6,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -8195,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C7,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -8213,7 +8293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C8,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -8231,7 +8311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C9,'Journal de travail'!$C$7:$C$532)*60</f>
         <v>0</v>
@@ -8249,7 +8329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="B10">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C10,'Journal de travail'!$D$7:$D$532)</f>
         <v>15</v>
@@ -8263,7 +8343,7 @@
         <v>1.0416666666666666E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="B11">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C11,'Journal de travail'!$D$7:$D$532)</f>
         <v>25</v>
@@ -8277,16 +8357,16 @@
         <v>1.7361111111111112E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="C12" s="26" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="46">
         <f>SUM(D4:D11)</f>
-        <v>6.9444444444444448E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.1736111111111111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="D14" s="50"/>
     </row>
   </sheetData>
@@ -8296,12 +8376,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8512,20 +8594,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
+    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8550,14 +8635,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
-    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Journal-de-Travail_MatiasDenis.xlsx
+++ b/Journal-de-Travail_MatiasDenis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_README\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32DFDC-36AC-49CA-9C46-E8AB8E886B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4DB2D6-7938-485D-8819-35B3772D5A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32040" yWindow="1020" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -186,6 +186,29 @@
   </si>
   <si>
     <t>Correction de l'arborescence des fichiers et importation réussie de la bibliothèque complète (6 livres) en format binaire (MEDIUMBLOB) dans MySQL via le BookSeeder.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refactorisation complète du </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BooksController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pour répondre aux exigences du projet ReadME : implémentation du tri par date d'ajout pour la liste des livres , intégration du support pour le contenu binaire (BLOB) dans la méthode d'affichage et nettoyage des champs obsolètes (pdf_link, image_path).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1085,7 +1108,7 @@
                   <c:v>0.10416666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.1666666666666664E-2</c:v>
+                  <c:v>6.25E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2063,7 +2086,7 @@
       </c>
       <c r="C3" s="25" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 9 heurs 9 minutes</v>
+        <v>0 jours 9 heurs 40 minutes</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="3"/>
@@ -2082,11 +2105,11 @@
       </c>
       <c r="D4" s="25">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E4" s="52">
         <f>SUM(C4:D4)</f>
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2275,13 +2298,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="63">
       <c r="A13" s="18"/>
-      <c r="B13" s="40"/>
+      <c r="B13" s="40">
+        <v>46062</v>
+      </c>
       <c r="C13" s="36"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="48"/>
+      <c r="D13" s="44">
+        <v>30</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>36</v>
+      </c>
       <c r="G13" s="20"/>
       <c r="M13" t="s">
         <v>8</v>
@@ -8246,7 +8277,7 @@
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C5" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8254,7 +8285,7 @@
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>4.1666666666666664E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8363,7 +8394,7 @@
       </c>
       <c r="D12" s="46">
         <f>SUM(D4:D11)</f>
-        <v>0.1736111111111111</v>
+        <v>0.19444444444444445</v>
       </c>
     </row>
     <row r="14" spans="1:4">

--- a/Journal-de-Travail_MatiasDenis.xlsx
+++ b/Journal-de-Travail_MatiasDenis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projet_README\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pb58unc\Desktop\P_AppMobile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4DB2D6-7938-485D-8819-35B3772D5A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB8D2E6-DAAD-442E-8670-DFC4E34C143C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32040" yWindow="1020" windowWidth="21600" windowHeight="11385" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6CC57B32-2488-5244-B7A6-FB7E808234AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal de travail" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -1108,7 +1108,7 @@
                   <c:v>0.10416666666666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.25E-2</c:v>
+                  <c:v>0.2048611111111111</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1126,7 +1126,7 @@
                   <c:v>1.0416666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.7361111111111112E-2</c:v>
+                  <c:v>5.2083333333333336E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C3" s="25" t="str">
         <f>INT(E4/1440)&amp;" jours "&amp;INT(MOD(E4/1440,1)*24)&amp;" heurs "&amp;INT(MOD(MOD(E4/1440,1)*24,1)*60)&amp;" minutes"</f>
-        <v>0 jours 9 heurs 40 minutes</v>
+        <v>0 jours 19 heurs 55 minutes</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="3"/>
@@ -2101,15 +2101,15 @@
       <c r="B4" s="5"/>
       <c r="C4" s="25">
         <f>SUBTOTAL(9,$C$7:$C$531)*60</f>
-        <v>420</v>
+        <v>960</v>
       </c>
       <c r="D4" s="25">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="E4" s="52">
         <f>SUM(C4:D4)</f>
-        <v>580</v>
+        <v>1195</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="7"/>
@@ -2325,10 +2325,21 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="B14" s="39"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="43"/>
-      <c r="F14" s="48"/>
+      <c r="B14" s="39">
+        <v>46076</v>
+      </c>
+      <c r="C14" s="35">
+        <v>3</v>
+      </c>
+      <c r="D14" s="43">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>32</v>
+      </c>
       <c r="G14" s="17"/>
       <c r="M14" t="s">
         <v>24</v>
@@ -2342,11 +2353,21 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="18"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="48"/>
+      <c r="B15" s="40">
+        <v>46083</v>
+      </c>
+      <c r="C15" s="36">
+        <v>3</v>
+      </c>
+      <c r="D15" s="44">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>32</v>
+      </c>
       <c r="G15" s="20"/>
       <c r="M15" t="s">
         <v>25</v>
@@ -2359,9 +2380,18 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="B16" s="39"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="39">
+        <v>46090</v>
+      </c>
+      <c r="C16" s="35">
+        <v>3</v>
+      </c>
+      <c r="D16" s="43">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
       <c r="F16" s="48"/>
       <c r="G16" s="17"/>
       <c r="O16">
@@ -8273,11 +8303,11 @@
     <row r="5" spans="1:4">
       <c r="A5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$C$7:$C$532)*60</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B5">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C5,'Journal de travail'!$D$7:$D$532)</f>
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C5" s="53" t="str">
         <f>'Journal de travail'!M9</f>
@@ -8285,7 +8315,7 @@
       </c>
       <c r="D5" s="45">
         <f t="shared" ref="D5:D11" si="0">(A5+B5)/1440</f>
-        <v>6.25E-2</v>
+        <v>0.2048611111111111</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -8377,7 +8407,7 @@
     <row r="11" spans="1:4">
       <c r="B11">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Analyse!C11,'Journal de travail'!$D$7:$D$532)</f>
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C11" s="51" t="str">
         <f>'Journal de travail'!M15</f>
@@ -8385,7 +8415,7 @@
       </c>
       <c r="D11" s="45">
         <f t="shared" si="0"/>
-        <v>1.7361111111111112E-2</v>
+        <v>5.2083333333333336E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -8394,7 +8424,7 @@
       </c>
       <c r="D12" s="46">
         <f>SUM(D4:D11)</f>
-        <v>0.19444444444444445</v>
+        <v>0.37152777777777779</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -8407,14 +8437,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8625,23 +8653,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26488081-7094-48e3-a435-bbb366c5709a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb2b4dc0-5538-4988-a426-1e3bf3687743">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
-    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
-    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
-    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8666,9 +8691,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74326215-CB02-4E95-BFFB-9EC625B1BF0F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0453EC0E-0298-408B-815C-A1500DB4F5E9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="be0d3259-a7ce-4623-88ec-81594dfcbc1c"/>
+    <ds:schemaRef ds:uri="99ffe1f3-7857-457f-add0-5bdef636f38d"/>
+    <ds:schemaRef ds:uri="26488081-7094-48e3-a435-bbb366c5709a"/>
+    <ds:schemaRef ds:uri="eb2b4dc0-5538-4988-a426-1e3bf3687743"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>